--- a/Assets/Excel/scavenge.xlsx
+++ b/Assets/Excel/scavenge.xlsx
@@ -1,16 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="21525" windowHeight="12270" activeTab="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="works" sheetId="1" r:id="rId2"/>
-    <sheet name="actions" sheetId="2" r:id="rId3"/>
-    <sheet name="loot" sheetId="3" r:id="rId4"/>
+    <sheet name="works" sheetId="1" r:id="rId1"/>
+    <sheet name="actions" sheetId="2" r:id="rId2"/>
+    <sheet name="loot" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="107">
   <si>
     <t>工作ID</t>
   </si>
@@ -335,10 +354,1169 @@
 </sst>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="2" width="8.875" customWidth="1"/>
+    <col min="3" max="3" width="13.75" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="6" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="19.125" customWidth="1"/>
+    <col min="9" max="10" width="18.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -370,7 +1548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -402,7 +1580,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -435,13 +1613,30 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="2" max="2" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="17.25" customWidth="1"/>
+    <col min="6" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="9.375" customWidth="1"/>
+    <col min="8" max="8" width="19.375" customWidth="1"/>
+    <col min="9" max="9" width="69.125" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -473,7 +1668,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -505,7 +1700,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -537,7 +1732,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -569,7 +1764,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -601,7 +1796,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -633,7 +1828,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -665,7 +1860,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>72</v>
       </c>
@@ -698,13 +1893,25 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="8.125" customWidth="1"/>
+    <col min="5" max="6" width="8.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -724,7 +1931,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -744,7 +1951,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -764,7 +1971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -784,7 +1991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -804,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -824,7 +2031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -844,7 +2051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -864,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -884,7 +2091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -904,7 +2111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -924,7 +2131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -944,7 +2151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -964,7 +2171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -984,7 +2191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -1004,7 +2211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -1024,7 +2231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -1044,7 +2251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>54</v>
       </c>
@@ -1064,7 +2271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -1084,7 +2291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -1104,7 +2311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1124,7 +2331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -1144,7 +2351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -1164,7 +2371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -1184,7 +2391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>60</v>
       </c>
@@ -1204,7 +2411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -1224,7 +2431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -1244,7 +2451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -1264,7 +2471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>66</v>
       </c>
@@ -1284,7 +2491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -1304,7 +2511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>66</v>
       </c>
@@ -1324,7 +2531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -1344,7 +2551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -1364,7 +2571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -1384,7 +2591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>72</v>
       </c>
@@ -1404,7 +2611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -1424,7 +2631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>72</v>
       </c>
@@ -1445,5 +2652,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Excel/scavenge.xlsx
+++ b/Assets/Excel/scavenge.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>工作ID</t>
   </si>
@@ -84,18 +84,6 @@
     <t>#2A4838</t>
   </si>
   <si>
-    <t>woodcutting</t>
-  </si>
-  <si>
-    <t>砍树</t>
-  </si>
-  <si>
-    <t>黑松林</t>
-  </si>
-  <si>
-    <t>#324030</t>
-  </si>
-  <si>
     <t>动作ID</t>
   </si>
   <si>
@@ -126,6 +114,12 @@
     <t>缩略图颜色</t>
   </si>
   <si>
+    <t>消耗道具ID</t>
+  </si>
+  <si>
+    <t>消耗数量</t>
+  </si>
+  <si>
     <t>workId</t>
   </si>
   <si>
@@ -153,6 +147,12 @@
     <t>thumbColor</t>
   </si>
   <si>
+    <t>costItemId</t>
+  </si>
+  <si>
+    <t>costAmount</t>
+  </si>
+  <si>
     <t>scavenge_gate</t>
   </si>
   <si>
@@ -168,6 +168,9 @@
     <t>进村的岔路口总有人掉东西。破布、空瓶最多，适合刚落脚的新手。</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>scavenge_street</t>
   </si>
   <si>
@@ -258,78 +261,6 @@
     <t>#585040</t>
   </si>
   <si>
-    <t>woodcut_pine</t>
-  </si>
-  <si>
-    <t>pine</t>
-  </si>
-  <si>
-    <t>短松</t>
-  </si>
-  <si>
-    <t>短松 · 伐木</t>
-  </si>
-  <si>
-    <t>林缘最常见的短松，长得快、好砍，专出松木。</t>
-  </si>
-  <si>
-    <t>#4A5C40</t>
-  </si>
-  <si>
-    <t>woodcut_birch</t>
-  </si>
-  <si>
-    <t>birch</t>
-  </si>
-  <si>
-    <t>白桦</t>
-  </si>
-  <si>
-    <t>白桦 · 伐木</t>
-  </si>
-  <si>
-    <t>溪边白桦树皮银白，伐倒后得桦木，比松木更适合做细工。</t>
-  </si>
-  <si>
-    <t>#C8B890</t>
-  </si>
-  <si>
-    <t>woodcut_oak</t>
-  </si>
-  <si>
-    <t>oak</t>
-  </si>
-  <si>
-    <t>橡树</t>
-  </si>
-  <si>
-    <t>橡树 · 伐木</t>
-  </si>
-  <si>
-    <t>林中层橡树粗壮，斧痕深一寸才见木心，产出沉实的橡木。</t>
-  </si>
-  <si>
-    <t>#5C4030</t>
-  </si>
-  <si>
-    <t>woodcut_ironwood</t>
-  </si>
-  <si>
-    <t>ironwood</t>
-  </si>
-  <si>
-    <t>铁木</t>
-  </si>
-  <si>
-    <t>铁木 · 伐木</t>
-  </si>
-  <si>
-    <t>黑松林深处的铁木，斧子咬进去像砍石头；慢，但每棵必出铁木。</t>
-  </si>
-  <si>
-    <t>#383028</t>
-  </si>
-  <si>
     <t>道具ID</t>
   </si>
   <si>
@@ -415,27 +346,6 @@
   </si>
   <si>
     <t>炉渣</t>
-  </si>
-  <si>
-    <t>pine_log</t>
-  </si>
-  <si>
-    <t>松木</t>
-  </si>
-  <si>
-    <t>birch_log</t>
-  </si>
-  <si>
-    <t>桦木</t>
-  </si>
-  <si>
-    <t>oak_log</t>
-  </si>
-  <si>
-    <t>橡木</t>
-  </si>
-  <si>
-    <t>ironwood_log</t>
   </si>
 </sst>
 </file>
@@ -536,38 +446,6 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4">
-        <v>40</v>
-      </c>
-      <c r="F4">
-        <v>20</v>
-      </c>
-      <c r="G4">
-        <v>40</v>
-      </c>
-      <c r="H4">
-        <v>20</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -580,34 +458,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>34</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>35</v>
-      </c>
-      <c r="I1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2">
@@ -615,30 +499,36 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>40</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>41</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>42</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>43</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>44</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>45</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>46</v>
       </c>
     </row>
@@ -673,22 +563,28 @@
       <c r="J3" t="s">
         <v>23</v>
       </c>
+      <c r="K3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F4">
         <v>4</v>
@@ -700,27 +596,33 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J4" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="K4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -732,27 +634,33 @@
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J5" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="K5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -764,27 +672,33 @@
         <v>6</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="K6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -796,27 +710,33 @@
         <v>9</v>
       </c>
       <c r="I7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J7" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="K7" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8">
         <v>9</v>
@@ -828,138 +748,16 @@
         <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
         <v>82</v>
       </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F9">
-        <v>4</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-      <c r="G10">
-        <v>9</v>
-      </c>
-      <c r="H10">
-        <v>3</v>
-      </c>
-      <c r="I10" t="s">
-        <v>92</v>
-      </c>
-      <c r="J10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11">
-        <v>6.5</v>
-      </c>
-      <c r="G11">
-        <v>14</v>
-      </c>
-      <c r="H11">
-        <v>6</v>
-      </c>
-      <c r="I11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12">
-        <v>9</v>
-      </c>
-      <c r="G12">
-        <v>22</v>
-      </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="I12" t="s">
-        <v>104</v>
-      </c>
-      <c r="J12" t="s">
-        <v>105</v>
+      <c r="K8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -971,42 +769,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D1" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="E1" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="F1" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="F2" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -1014,10 +812,10 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="D3">
         <v>0.88</v>
@@ -1034,10 +832,10 @@
         <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D4">
         <v>0.42</v>
@@ -1054,10 +852,10 @@
         <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D5">
         <v>0.3</v>
@@ -1074,10 +872,10 @@
         <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D6">
         <v>0.08</v>
@@ -1094,10 +892,10 @@
         <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D7">
         <v>0.005</v>
@@ -1111,13 +909,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="D8">
         <v>0.65</v>
@@ -1131,13 +929,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D9">
         <v>0.5</v>
@@ -1151,13 +949,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D10">
         <v>0.45</v>
@@ -1171,13 +969,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="D11">
         <v>0.18</v>
@@ -1191,13 +989,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D12">
         <v>0.22</v>
@@ -1211,13 +1009,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="D13">
         <v>0.05</v>
@@ -1231,13 +1029,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D14">
         <v>0.01</v>
@@ -1251,13 +1049,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="D15">
         <v>0.72</v>
@@ -1271,13 +1069,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D16">
         <v>0.78</v>
@@ -1291,13 +1089,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D17">
         <v>0.4</v>
@@ -1311,13 +1109,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="D18">
         <v>0.15</v>
@@ -1331,13 +1129,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="D19">
         <v>0.14</v>
@@ -1351,13 +1149,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="D20">
         <v>0.02</v>
@@ -1371,13 +1169,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D21">
         <v>0.015</v>
@@ -1391,13 +1189,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D22">
         <v>0.58</v>
@@ -1411,13 +1209,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D23">
         <v>0.38</v>
@@ -1431,13 +1229,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="D24">
         <v>0.25</v>
@@ -1451,13 +1249,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="D25">
         <v>0.16</v>
@@ -1471,13 +1269,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="D26">
         <v>0.06</v>
@@ -1491,13 +1289,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D27">
         <v>0.04</v>
@@ -1511,13 +1309,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="D28">
         <v>0.7</v>
@@ -1531,13 +1329,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="D29">
         <v>0.45</v>
@@ -1551,13 +1349,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D30">
         <v>0.25</v>
@@ -1571,13 +1369,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="D31">
         <v>0.12</v>
@@ -1591,13 +1389,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D32">
         <v>0.02</v>
@@ -1611,13 +1409,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="D33">
         <v>0.12</v>
@@ -1631,13 +1429,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="D34">
         <v>0.1</v>
@@ -1651,13 +1449,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="D35">
         <v>0.2</v>
@@ -1671,13 +1469,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="D36">
         <v>0.18</v>
@@ -1691,13 +1489,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="D37">
         <v>0.08</v>
@@ -1706,86 +1504,6 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" t="s">
-        <v>135</v>
-      </c>
-      <c r="C38" t="s">
-        <v>136</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>88</v>
-      </c>
-      <c r="B39" t="s">
-        <v>137</v>
-      </c>
-      <c r="C39" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>94</v>
-      </c>
-      <c r="B40" t="s">
-        <v>139</v>
-      </c>
-      <c r="C40" t="s">
-        <v>140</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>100</v>
-      </c>
-      <c r="B41" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" t="s">
-        <v>102</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excel/scavenge.xlsx
+++ b/Assets/Excel/scavenge.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
   <si>
     <t>工作ID</t>
   </si>
@@ -96,6 +96,9 @@
     <t>地区名称</t>
   </si>
   <si>
+    <t>子地点名</t>
+  </si>
+  <si>
     <t>卡片标题</t>
   </si>
   <si>
@@ -129,6 +132,9 @@
     <t>sceneName</t>
   </si>
   <si>
+    <t>spotName</t>
+  </si>
+  <si>
     <t>displayName</t>
   </si>
   <si>
@@ -153,7 +159,7 @@
     <t>costAmount</t>
   </si>
   <si>
-    <t>scavenge_gate</t>
+    <t>scavenge_gate_fork</t>
   </si>
   <si>
     <t>gate</t>
@@ -162,7 +168,10 @@
     <t>村口</t>
   </si>
   <si>
-    <t>村口 · 拾荒</t>
+    <t>岔路口</t>
+  </si>
+  <si>
+    <t>村口 · 岔路口</t>
   </si>
   <si>
     <t>进村的岔路口总有人掉东西。破布、空瓶最多，适合刚落脚的新手。</t>
@@ -171,7 +180,37 @@
     <t/>
   </si>
   <si>
-    <t>scavenge_street</t>
+    <t>scavenge_gate_wang</t>
+  </si>
+  <si>
+    <t>老王家</t>
+  </si>
+  <si>
+    <t>村口 · 老王家</t>
+  </si>
+  <si>
+    <t>老王家篱笆外常堆着换下来的破布和木屑，手快就有。</t>
+  </si>
+  <si>
+    <t>#324838</t>
+  </si>
+  <si>
+    <t>scavenge_gate_li</t>
+  </si>
+  <si>
+    <t>老李家</t>
+  </si>
+  <si>
+    <t>村口 · 老李家</t>
+  </si>
+  <si>
+    <t>老李家门前晾衣绳下，空瓶和褪色铜币比别处多一点点。</t>
+  </si>
+  <si>
+    <t>#3A4838</t>
+  </si>
+  <si>
+    <t>scavenge_street_corner</t>
   </si>
   <si>
     <t>street</t>
@@ -180,16 +219,46 @@
     <t>街道</t>
   </si>
   <si>
-    <t>街道 · 扫街角</t>
+    <t>街角</t>
+  </si>
+  <si>
+    <t>街道 · 街角</t>
   </si>
   <si>
     <t>早市散场后，街角堆着果皮和破筐。铜钉、褪色铜币比村口常见些。</t>
   </si>
   <si>
-    <t>#3A4838</t>
-  </si>
-  <si>
-    <t>scavenge_barn</t>
+    <t>scavenge_street_market</t>
+  </si>
+  <si>
+    <t>早市残骸</t>
+  </si>
+  <si>
+    <t>街道 · 早市残骸</t>
+  </si>
+  <si>
+    <t>摊贩收摊后留下的破筐和烂菜叶底下，偶尔能翻出铜钉。</t>
+  </si>
+  <si>
+    <t>#424838</t>
+  </si>
+  <si>
+    <t>scavenge_street_alley</t>
+  </si>
+  <si>
+    <t>后巷</t>
+  </si>
+  <si>
+    <t>街道 · 后巷</t>
+  </si>
+  <si>
+    <t>店铺后巷阴暗潮湿，碎木和空瓶堆在墙角，得小心碎瓷片。</t>
+  </si>
+  <si>
+    <t>#384838</t>
+  </si>
+  <si>
+    <t>scavenge_barn_heap</t>
   </si>
   <si>
     <t>barn</t>
@@ -198,7 +267,10 @@
     <t>谷仓后</t>
   </si>
   <si>
-    <t>谷仓后 · 翻废料</t>
+    <t>废料堆</t>
+  </si>
+  <si>
+    <t>谷仓后 · 废料堆</t>
   </si>
   <si>
     <t>谷仓后面堆着村民倒掉的杂物。碎木、破布多，偶尔翻出药草芽。</t>
@@ -207,7 +279,37 @@
     <t>#504838</t>
   </si>
   <si>
-    <t>scavenge_stream</t>
+    <t>scavenge_barn_shed</t>
+  </si>
+  <si>
+    <t>储物棚</t>
+  </si>
+  <si>
+    <t>谷仓后 · 储物棚</t>
+  </si>
+  <si>
+    <t>棚子底下藏着去年没收干净的麻袋和碎木，药草芽概率略高。</t>
+  </si>
+  <si>
+    <t>#584838</t>
+  </si>
+  <si>
+    <t>scavenge_barn_fence</t>
+  </si>
+  <si>
+    <t>篱笆边</t>
+  </si>
+  <si>
+    <t>谷仓后 · 篱笆边</t>
+  </si>
+  <si>
+    <t>篱笆被风吹垮了一截，破布和空瓶卡在木刺之间。</t>
+  </si>
+  <si>
+    <t>#4C4838</t>
+  </si>
+  <si>
+    <t>scavenge_stream_shallow</t>
   </si>
   <si>
     <t>stream</t>
@@ -216,7 +318,10 @@
     <t>溪滩</t>
   </si>
   <si>
-    <t>溪滩 · 捞漂物</t>
+    <t>浅水区</t>
+  </si>
+  <si>
+    <t>溪滩 · 浅水区</t>
   </si>
   <si>
     <t>萤溪涨水会把上游的东西冲下来。空瓶、护符比陆地好捞。</t>
@@ -225,7 +330,22 @@
     <t>#2E5850</t>
   </si>
   <si>
-    <t>scavenge_forge_alley</t>
+    <t>scavenge_stream_eddies</t>
+  </si>
+  <si>
+    <t>回水湾</t>
+  </si>
+  <si>
+    <t>溪滩 · 回水湾</t>
+  </si>
+  <si>
+    <t>回水湾里打着旋的杂物多，护符和星尘碎屑比浅水区更常见。</t>
+  </si>
+  <si>
+    <t>#365850</t>
+  </si>
+  <si>
+    <t>scavenge_forge_slag</t>
   </si>
   <si>
     <t>forge_alley</t>
@@ -234,7 +354,10 @@
     <t>铁砧巷</t>
   </si>
   <si>
-    <t>铁砧巷 · 捡炉渣</t>
+    <t>炉渣堆</t>
+  </si>
+  <si>
+    <t>铁砧巷 · 炉渣堆</t>
   </si>
   <si>
     <t>铁匠铺后巷，炉渣和废钉随地都是。想攒锻造料，这里是捷径。</t>
@@ -243,7 +366,22 @@
     <t>#484038</t>
   </si>
   <si>
-    <t>scavenge_monument</t>
+    <t>scavenge_forge_scrap</t>
+  </si>
+  <si>
+    <t>张铁匠铺后</t>
+  </si>
+  <si>
+    <t>铁砧巷 · 张铁匠铺后</t>
+  </si>
+  <si>
+    <t>张铁匠铺后门外的废铁筐，炉渣和铜钉尤其多。</t>
+  </si>
+  <si>
+    <t>#504038</t>
+  </si>
+  <si>
+    <t>scavenge_monument_base</t>
   </si>
   <si>
     <t>monument</t>
@@ -252,13 +390,31 @@
     <t>坠星碑</t>
   </si>
   <si>
-    <t>坠星碑 · 耙星屑</t>
+    <t>碑基</t>
+  </si>
+  <si>
+    <t>坠星碑 · 碑基</t>
   </si>
   <si>
     <t>当年坠星留下的碑旁，泥土里仍嵌着微光颗粒。慢，但星尘碎屑概率最高。</t>
   </si>
   <si>
     <t>#585040</t>
+  </si>
+  <si>
+    <t>scavenge_monument_field</t>
+  </si>
+  <si>
+    <t>星屑地</t>
+  </si>
+  <si>
+    <t>坠星碑 · 星屑地</t>
+  </si>
+  <si>
+    <t>碑外一圈被星尘染色的裸地，耙起来费时，但护符与碎屑都不缺。</t>
+  </si>
+  <si>
+    <t>#605040</t>
   </si>
   <si>
     <t>道具ID</t>
@@ -493,232 +649,253 @@
       <c r="L1" t="s">
         <v>35</v>
       </c>
+      <c r="M1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="M2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3">
         <v>3.5</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>6</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="I3" t="s">
-        <v>51</v>
-      </c>
       <c r="J3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="K3" t="s">
-        <v>52</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" t="s">
         <v>55</v>
       </c>
-      <c r="E4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>8</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4">
+      <c r="M4">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>62</v>
       </c>
-      <c r="F5">
-        <v>5</v>
+      <c r="F5" t="s">
+        <v>63</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5" t="s">
-        <v>63</v>
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
       </c>
       <c r="J5" t="s">
         <v>64</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L5">
+        <v>65</v>
+      </c>
+      <c r="L5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
+        <v>69</v>
+      </c>
+      <c r="F6" t="s">
+        <v>70</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6" t="s">
-        <v>69</v>
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K6" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6">
+        <v>65</v>
+      </c>
+      <c r="L6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" t="s">
         <v>73</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>74</v>
       </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
       <c r="G7">
-        <v>18</v>
+        <v>4.5</v>
       </c>
       <c r="H7">
         <v>9</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7" t="s">
         <v>75</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>76</v>
       </c>
-      <c r="K7" t="s">
-        <v>52</v>
-      </c>
-      <c r="L7">
+      <c r="L7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
     </row>
@@ -730,33 +907,405 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" t="s">
         <v>78</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>79</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
         <v>80</v>
       </c>
-      <c r="F8">
+      <c r="K8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <v>12</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10">
+        <v>5.5</v>
+      </c>
+      <c r="H10">
+        <v>13</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K10" t="s">
+        <v>93</v>
+      </c>
+      <c r="L10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>12</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11" t="s">
+        <v>97</v>
+      </c>
+      <c r="K11" t="s">
+        <v>98</v>
+      </c>
+      <c r="L11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+      <c r="H12">
+        <v>16</v>
+      </c>
+      <c r="I12">
+        <v>6</v>
+      </c>
+      <c r="J12" t="s">
+        <v>104</v>
+      </c>
+      <c r="K12" t="s">
+        <v>105</v>
+      </c>
+      <c r="L12" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13">
+        <v>8</v>
+      </c>
+      <c r="H13">
+        <v>18</v>
+      </c>
+      <c r="I13">
+        <v>6</v>
+      </c>
+      <c r="J13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K13" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" t="s">
+        <v>115</v>
+      </c>
+      <c r="G14">
+        <v>6</v>
+      </c>
+      <c r="H14">
+        <v>18</v>
+      </c>
+      <c r="I14">
         <v>9</v>
       </c>
-      <c r="G8">
+      <c r="J14" t="s">
+        <v>116</v>
+      </c>
+      <c r="K14" t="s">
+        <v>117</v>
+      </c>
+      <c r="L14" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15">
+        <v>6.5</v>
+      </c>
+      <c r="H15">
+        <v>19</v>
+      </c>
+      <c r="I15">
+        <v>9</v>
+      </c>
+      <c r="J15" t="s">
+        <v>121</v>
+      </c>
+      <c r="K15" t="s">
+        <v>122</v>
+      </c>
+      <c r="L15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16">
+        <v>9</v>
+      </c>
+      <c r="H16">
         <v>24</v>
       </c>
-      <c r="H8">
+      <c r="I16">
         <v>12</v>
       </c>
-      <c r="I8" t="s">
-        <v>81</v>
-      </c>
-      <c r="J8" t="s">
-        <v>82</v>
-      </c>
-      <c r="K8" t="s">
-        <v>52</v>
-      </c>
-      <c r="L8">
+      <c r="J16" t="s">
+        <v>128</v>
+      </c>
+      <c r="K16" t="s">
+        <v>129</v>
+      </c>
+      <c r="L16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F17" t="s">
+        <v>132</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <v>26</v>
+      </c>
+      <c r="I17">
+        <v>12</v>
+      </c>
+      <c r="J17" t="s">
+        <v>133</v>
+      </c>
+      <c r="K17" t="s">
+        <v>134</v>
+      </c>
+      <c r="L17" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17">
         <v>0</v>
       </c>
     </row>
@@ -772,50 +1321,50 @@
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="C1" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="D1" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="E1" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="F1" t="s">
-        <v>87</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="F2" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="D3">
         <v>0.88</v>
@@ -829,13 +1378,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="D4">
         <v>0.42</v>
@@ -849,13 +1398,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>151</v>
       </c>
       <c r="D5">
         <v>0.3</v>
@@ -869,13 +1418,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="D6">
         <v>0.08</v>
@@ -889,13 +1438,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D7">
         <v>0.005</v>
@@ -909,36 +1458,36 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="D8">
-        <v>0.65</v>
+        <v>0.92</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -949,16 +1498,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>149</v>
       </c>
       <c r="D10">
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -969,16 +1518,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="D11">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -989,16 +1538,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="D12">
-        <v>0.22</v>
+        <v>0.62</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1009,16 +1558,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="D13">
-        <v>0.05</v>
+        <v>0.7</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1029,16 +1578,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D14">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1049,36 +1598,36 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="D15">
-        <v>0.72</v>
+        <v>0.22</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="D16">
-        <v>0.78</v>
+        <v>0.008</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1089,16 +1638,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="D17">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1109,16 +1658,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="D18">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1129,16 +1678,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="D19">
-        <v>0.14</v>
+        <v>0.45</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1149,16 +1698,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="D20">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1169,16 +1718,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D21">
-        <v>0.015</v>
+        <v>0.22</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1189,16 +1738,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="D22">
-        <v>0.58</v>
+        <v>0.05</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1209,16 +1758,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="D23">
-        <v>0.38</v>
+        <v>0.01</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1229,16 +1778,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="D24">
-        <v>0.25</v>
+        <v>0.58</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1249,16 +1798,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="D25">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1269,16 +1818,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="D26">
-        <v>0.06</v>
+        <v>0.46</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1289,16 +1838,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="D27">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1309,16 +1858,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="D28">
-        <v>0.7</v>
+        <v>0.18</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1329,16 +1878,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="D29">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1349,16 +1898,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>149</v>
       </c>
       <c r="D30">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1369,16 +1918,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="D31">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1389,16 +1938,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="D32">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1412,13 +1961,13 @@
         <v>77</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="C33" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D33">
-        <v>0.12</v>
+        <v>0.012</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1429,36 +1978,36 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="D34">
-        <v>0.1</v>
+        <v>0.72</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="D35">
-        <v>0.2</v>
+        <v>0.78</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1469,16 +2018,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="D36">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1489,21 +2038,881 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" t="s">
+        <v>157</v>
+      </c>
+      <c r="D37">
+        <v>0.15</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38">
+        <v>0.14</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" t="s">
+        <v>160</v>
+      </c>
+      <c r="C39" t="s">
+        <v>161</v>
+      </c>
+      <c r="D39">
+        <v>0.02</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40">
+        <v>0.015</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" t="s">
+        <v>151</v>
+      </c>
+      <c r="D41">
+        <v>0.7</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" t="s">
+        <v>146</v>
+      </c>
+      <c r="C42" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42">
+        <v>0.6</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" t="s">
+        <v>158</v>
+      </c>
+      <c r="C43" t="s">
+        <v>159</v>
+      </c>
+      <c r="D43">
+        <v>0.2</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" t="s">
+        <v>156</v>
+      </c>
+      <c r="C44" t="s">
+        <v>157</v>
+      </c>
+      <c r="D44">
+        <v>0.12</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" t="s">
+        <v>160</v>
+      </c>
+      <c r="C45" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45">
+        <v>0.025</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" t="s">
+        <v>146</v>
+      </c>
+      <c r="C46" t="s">
+        <v>147</v>
+      </c>
+      <c r="D46">
+        <v>0.8</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B47" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47">
+        <v>0.48</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" t="s">
+        <v>151</v>
+      </c>
+      <c r="D48">
+        <v>0.5</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C49" t="s">
+        <v>159</v>
+      </c>
+      <c r="D49">
+        <v>0.1</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" t="s">
+        <v>152</v>
+      </c>
+      <c r="C50" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50">
+        <v>0.1</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" t="s">
+        <v>148</v>
+      </c>
+      <c r="C51" t="s">
+        <v>149</v>
+      </c>
+      <c r="D51">
+        <v>0.58</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" t="s">
+        <v>151</v>
+      </c>
+      <c r="D52">
+        <v>0.38</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" t="s">
+        <v>157</v>
+      </c>
+      <c r="D53">
+        <v>0.25</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54">
+        <v>0.16</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" t="s">
+        <v>160</v>
+      </c>
+      <c r="C55" t="s">
+        <v>161</v>
+      </c>
+      <c r="D55">
+        <v>0.06</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" t="s">
+        <v>154</v>
+      </c>
+      <c r="C56" t="s">
+        <v>155</v>
+      </c>
+      <c r="D56">
+        <v>0.04</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
         <v>106</v>
       </c>
-      <c r="C37" t="s">
-        <v>107</v>
-      </c>
-      <c r="D37">
+      <c r="B57" t="s">
+        <v>148</v>
+      </c>
+      <c r="C57" t="s">
+        <v>149</v>
+      </c>
+      <c r="D57">
+        <v>0.5</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>106</v>
+      </c>
+      <c r="B58" t="s">
+        <v>160</v>
+      </c>
+      <c r="C58" t="s">
+        <v>161</v>
+      </c>
+      <c r="D58">
+        <v>0.1</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59">
+        <v>0.22</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>106</v>
+      </c>
+      <c r="B60" t="s">
+        <v>158</v>
+      </c>
+      <c r="C60" t="s">
+        <v>159</v>
+      </c>
+      <c r="D60">
+        <v>0.14</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>106</v>
+      </c>
+      <c r="B61" t="s">
+        <v>154</v>
+      </c>
+      <c r="C61" t="s">
+        <v>155</v>
+      </c>
+      <c r="D61">
+        <v>0.055</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>111</v>
+      </c>
+      <c r="B62" t="s">
+        <v>162</v>
+      </c>
+      <c r="C62" t="s">
+        <v>163</v>
+      </c>
+      <c r="D62">
+        <v>0.7</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>111</v>
+      </c>
+      <c r="B63" t="s">
+        <v>156</v>
+      </c>
+      <c r="C63" t="s">
+        <v>157</v>
+      </c>
+      <c r="D63">
+        <v>0.45</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>111</v>
+      </c>
+      <c r="B64" t="s">
+        <v>150</v>
+      </c>
+      <c r="C64" t="s">
+        <v>151</v>
+      </c>
+      <c r="D64">
+        <v>0.25</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" t="s">
+        <v>152</v>
+      </c>
+      <c r="C65" t="s">
+        <v>153</v>
+      </c>
+      <c r="D65">
+        <v>0.12</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>111</v>
+      </c>
+      <c r="B66" t="s">
+        <v>154</v>
+      </c>
+      <c r="C66" t="s">
+        <v>155</v>
+      </c>
+      <c r="D66">
+        <v>0.02</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>118</v>
+      </c>
+      <c r="B67" t="s">
+        <v>162</v>
+      </c>
+      <c r="C67" t="s">
+        <v>163</v>
+      </c>
+      <c r="D67">
+        <v>0.75</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>118</v>
+      </c>
+      <c r="B68" t="s">
+        <v>156</v>
+      </c>
+      <c r="C68" t="s">
+        <v>157</v>
+      </c>
+      <c r="D68">
+        <v>0.52</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>118</v>
+      </c>
+      <c r="B69" t="s">
+        <v>150</v>
+      </c>
+      <c r="C69" t="s">
+        <v>151</v>
+      </c>
+      <c r="D69">
+        <v>0.18</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>118</v>
+      </c>
+      <c r="B70" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" t="s">
+        <v>155</v>
+      </c>
+      <c r="D70">
+        <v>0.025</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B71" t="s">
+        <v>154</v>
+      </c>
+      <c r="C71" t="s">
+        <v>155</v>
+      </c>
+      <c r="D71">
+        <v>0.12</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>123</v>
+      </c>
+      <c r="B72" t="s">
+        <v>160</v>
+      </c>
+      <c r="C72" t="s">
+        <v>161</v>
+      </c>
+      <c r="D72">
+        <v>0.1</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>123</v>
+      </c>
+      <c r="B73" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" t="s">
+        <v>157</v>
+      </c>
+      <c r="D73">
+        <v>0.2</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>123</v>
+      </c>
+      <c r="B74" t="s">
+        <v>162</v>
+      </c>
+      <c r="C74" t="s">
+        <v>163</v>
+      </c>
+      <c r="D74">
+        <v>0.18</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>123</v>
+      </c>
+      <c r="B75" t="s">
+        <v>158</v>
+      </c>
+      <c r="C75" t="s">
+        <v>159</v>
+      </c>
+      <c r="D75">
         <v>0.08</v>
       </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>130</v>
+      </c>
+      <c r="B76" t="s">
+        <v>154</v>
+      </c>
+      <c r="C76" t="s">
+        <v>155</v>
+      </c>
+      <c r="D76">
+        <v>0.14</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>130</v>
+      </c>
+      <c r="B77" t="s">
+        <v>160</v>
+      </c>
+      <c r="C77" t="s">
+        <v>161</v>
+      </c>
+      <c r="D77">
+        <v>0.12</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>130</v>
+      </c>
+      <c r="B78" t="s">
+        <v>156</v>
+      </c>
+      <c r="C78" t="s">
+        <v>157</v>
+      </c>
+      <c r="D78">
+        <v>0.16</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>130</v>
+      </c>
+      <c r="B79" t="s">
+        <v>162</v>
+      </c>
+      <c r="C79" t="s">
+        <v>163</v>
+      </c>
+      <c r="D79">
+        <v>0.14</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>130</v>
+      </c>
+      <c r="B80" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" t="s">
+        <v>159</v>
+      </c>
+      <c r="D80">
+        <v>0.06</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excel/scavenge.xlsx
+++ b/Assets/Excel/scavenge.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
   <si>
     <t>工作ID</t>
   </si>
@@ -111,7 +111,7 @@
     <t>解锁所需工作等级</t>
   </si>
   <si>
-    <t>描述</t>
+    <t>详情文案(右侧)</t>
   </si>
   <si>
     <t>缩略图颜色</t>
@@ -123,6 +123,15 @@
     <t>消耗数量</t>
   </si>
   <si>
+    <t>金币概率0~1</t>
+  </si>
+  <si>
+    <t>金币最少</t>
+  </si>
+  <si>
+    <t>金币最多</t>
+  </si>
+  <si>
     <t>workId</t>
   </si>
   <si>
@@ -159,6 +168,15 @@
     <t>costAmount</t>
   </si>
   <si>
+    <t>goldChance</t>
+  </si>
+  <si>
+    <t>goldMin</t>
+  </si>
+  <si>
+    <t>goldMax</t>
+  </si>
+  <si>
     <t>scavenge_gate_fork</t>
   </si>
   <si>
@@ -168,48 +186,78 @@
     <t>村口</t>
   </si>
   <si>
-    <t>岔路口</t>
-  </si>
-  <si>
-    <t>村口 · 岔路口</t>
-  </si>
-  <si>
-    <t>进村的岔路口总有人掉东西。破布、空瓶最多，适合刚落脚的新手。</t>
+    <t>村子岔路口</t>
+  </si>
+  <si>
+    <t>村口 · 村子岔路口</t>
+  </si>
+  <si>
+    <t>进出村的岔路口总有人掉东西。破布、空瓶最多，适合刚落脚的新手。</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>scavenge_gate_wang</t>
-  </si>
-  <si>
-    <t>老王家</t>
-  </si>
-  <si>
-    <t>村口 · 老王家</t>
-  </si>
-  <si>
-    <t>老王家篱笆外常堆着换下来的破布和木屑，手快就有。</t>
+    <t>scavenge_gate_ergou</t>
+  </si>
+  <si>
+    <t>二狗家</t>
+  </si>
+  <si>
+    <t>村口 · 二狗家</t>
+  </si>
+  <si>
+    <t>二狗家院子角落堆着破筐和破布，他家狗叫得凶，得手快。</t>
   </si>
   <si>
     <t>#324838</t>
   </si>
   <si>
-    <t>scavenge_gate_li</t>
-  </si>
-  <si>
-    <t>老李家</t>
-  </si>
-  <si>
-    <t>村口 · 老李家</t>
-  </si>
-  <si>
-    <t>老李家门前晾衣绳下，空瓶和褪色铜币比别处多一点点。</t>
+    <t>scavenge_gate_woodshed</t>
+  </si>
+  <si>
+    <t>废弃柴房</t>
+  </si>
+  <si>
+    <t>村口 · 废弃柴房</t>
+  </si>
+  <si>
+    <t>村口边上塌了半边的柴房，碎木和旧麻袋最好拣，当心朽木扎手。</t>
+  </si>
+  <si>
+    <t>#344838</t>
+  </si>
+  <si>
+    <t>scavenge_gate_well</t>
+  </si>
+  <si>
+    <t>老井边</t>
+  </si>
+  <si>
+    <t>村口 · 老井边</t>
+  </si>
+  <si>
+    <t>井台边湿滑，常能捞到空瓶和洗衣落下的破布，褪色铜币也比别处多一点。</t>
   </si>
   <si>
     <t>#3A4838</t>
   </si>
   <si>
+    <t>scavenge_gate_chief</t>
+  </si>
+  <si>
+    <t>村长家</t>
+  </si>
+  <si>
+    <t>村口 · 村长家</t>
+  </si>
+  <si>
+    <t>村长家门口管教严，篱笆外仍偶有铜币和空瓶，得赶在村人注意前捡完。</t>
+  </si>
+  <si>
+    <t>#404838</t>
+  </si>
+  <si>
     <t>scavenge_street_corner</t>
   </si>
   <si>
@@ -448,6 +496,12 @@
   </si>
   <si>
     <t>max</t>
+  </si>
+  <si>
+    <t>_empty</t>
+  </si>
+  <si>
+    <t>（无）</t>
   </si>
   <si>
     <t>rag</t>
@@ -652,66 +706,84 @@
       <c r="M1" t="s">
         <v>36</v>
       </c>
+      <c r="N1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M2" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>3.5</v>
@@ -723,36 +795,45 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K3" t="s">
         <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M3">
         <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0.18</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -764,185 +845,230 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M4">
         <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0.15</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M5">
         <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0.14</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K6" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M6">
         <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0.22</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G7">
         <v>4.5</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M7">
         <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0.2</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="K8" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="L8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M8">
         <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0.25</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
@@ -954,36 +1080,45 @@
         <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L9" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M9">
         <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0.22</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
@@ -995,51 +1130,60 @@
         <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G10">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="H10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0.28</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
         <v>4</v>
-      </c>
-      <c r="J10" t="s">
-        <v>92</v>
-      </c>
-      <c r="K10" t="s">
-        <v>93</v>
-      </c>
-      <c r="L10" t="s">
-        <v>55</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -1051,262 +1195,425 @@
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K11" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L11" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M11">
         <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0.3</v>
+      </c>
+      <c r="O11">
+        <v>2</v>
+      </c>
+      <c r="P11">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
       </c>
       <c r="C12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" t="s">
         <v>100</v>
       </c>
-      <c r="D12" t="s">
-        <v>101</v>
-      </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G12">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="H12">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K12" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M12">
         <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0.28</v>
+      </c>
+      <c r="O12">
+        <v>2</v>
+      </c>
+      <c r="P12">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
       <c r="C13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" t="s">
         <v>100</v>
       </c>
-      <c r="D13" t="s">
-        <v>101</v>
-      </c>
       <c r="E13" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K13" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L13" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M13">
         <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0.32</v>
+      </c>
+      <c r="O13">
+        <v>2</v>
+      </c>
+      <c r="P13">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G14">
+        <v>7</v>
+      </c>
+      <c r="H14">
+        <v>16</v>
+      </c>
+      <c r="I14">
         <v>6</v>
       </c>
-      <c r="H14">
-        <v>18</v>
-      </c>
-      <c r="I14">
-        <v>9</v>
-      </c>
       <c r="J14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="K14" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L14" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M14">
         <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0.35</v>
+      </c>
+      <c r="O14">
+        <v>2</v>
+      </c>
+      <c r="P14">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F15" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G15">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="H15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J15" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="L15" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M15">
         <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0.38</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F16" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G16">
+        <v>6</v>
+      </c>
+      <c r="H16">
+        <v>18</v>
+      </c>
+      <c r="I16">
         <v>9</v>
       </c>
-      <c r="H16">
-        <v>24</v>
-      </c>
-      <c r="I16">
-        <v>12</v>
-      </c>
       <c r="J16" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K16" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="M16">
         <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0.4</v>
+      </c>
+      <c r="O16">
+        <v>3</v>
+      </c>
+      <c r="P16">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E17" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F17" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G17">
+        <v>6.5</v>
+      </c>
+      <c r="H17">
+        <v>19</v>
+      </c>
+      <c r="I17">
+        <v>9</v>
+      </c>
+      <c r="J17" t="s">
+        <v>137</v>
+      </c>
+      <c r="K17" t="s">
+        <v>138</v>
+      </c>
+      <c r="L17" t="s">
+        <v>61</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0.42</v>
+      </c>
+      <c r="O17">
+        <v>3</v>
+      </c>
+      <c r="P17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" t="s">
+        <v>141</v>
+      </c>
+      <c r="E18" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" t="s">
+        <v>143</v>
+      </c>
+      <c r="G18">
+        <v>9</v>
+      </c>
+      <c r="H18">
+        <v>24</v>
+      </c>
+      <c r="I18">
+        <v>12</v>
+      </c>
+      <c r="J18" t="s">
+        <v>144</v>
+      </c>
+      <c r="K18" t="s">
+        <v>145</v>
+      </c>
+      <c r="L18" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0.45</v>
+      </c>
+      <c r="O18">
+        <v>4</v>
+      </c>
+      <c r="P18">
         <v>10</v>
       </c>
-      <c r="H17">
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F19" t="s">
+        <v>148</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+      <c r="H19">
         <v>26</v>
       </c>
-      <c r="I17">
+      <c r="I19">
         <v>12</v>
       </c>
-      <c r="J17" t="s">
-        <v>133</v>
-      </c>
-      <c r="K17" t="s">
-        <v>134</v>
-      </c>
-      <c r="L17" t="s">
-        <v>55</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
+      <c r="J19" t="s">
+        <v>149</v>
+      </c>
+      <c r="K19" t="s">
+        <v>150</v>
+      </c>
+      <c r="L19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0.48</v>
+      </c>
+      <c r="O19">
+        <v>4</v>
+      </c>
+      <c r="P19">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1321,53 +1628,53 @@
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="C1" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D1" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E1" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F1" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="F2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="D3">
-        <v>0.88</v>
+        <v>0.38</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1378,16 +1685,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="D4">
-        <v>0.42</v>
+        <v>0.88</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1398,16 +1705,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="D5">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1418,16 +1725,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="D6">
-        <v>0.08</v>
+        <v>0.3</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1438,16 +1745,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="D7">
-        <v>0.005</v>
+        <v>0.08</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1458,36 +1765,36 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D8">
-        <v>0.92</v>
+        <v>0.005</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D9">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1498,36 +1805,36 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="D10">
-        <v>0.28</v>
+        <v>0.92</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="D11">
-        <v>0.06</v>
+        <v>0.55</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1538,16 +1845,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D12">
-        <v>0.62</v>
+        <v>0.28</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1558,16 +1865,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="D13">
-        <v>0.7</v>
+        <v>0.06</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1578,16 +1885,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C14" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D14">
-        <v>0.14</v>
+        <v>0.42</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1598,16 +1905,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="C15" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D15">
-        <v>0.22</v>
+        <v>0.85</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1618,16 +1925,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C16" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D16">
-        <v>0.008</v>
+        <v>0.68</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1638,16 +1945,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="D17">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1658,16 +1965,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C18" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="D18">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1678,16 +1985,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D19">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1698,16 +2005,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D20">
-        <v>0.18</v>
+        <v>0.62</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1718,16 +2025,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C21" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D21">
-        <v>0.22</v>
+        <v>0.7</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1738,16 +2045,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C22" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D22">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1758,16 +2065,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="D23">
-        <v>0.01</v>
+        <v>0.22</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1781,13 +2088,13 @@
         <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D24">
-        <v>0.58</v>
+        <v>0.008</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1798,16 +2105,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D25">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1818,16 +2125,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C26" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D26">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1838,16 +2145,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C27" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D27">
-        <v>0.08</v>
+        <v>0.55</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1858,13 +2165,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C28" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D28">
         <v>0.18</v>
@@ -1881,13 +2188,13 @@
         <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="C29" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D29">
-        <v>0.68</v>
+        <v>0.25</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1901,13 +2208,13 @@
         <v>77</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="D30">
-        <v>0.52</v>
+        <v>0.006</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1918,16 +2225,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C31" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D31">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1938,16 +2245,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B32" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D32">
-        <v>0.2</v>
+        <v>0.65</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1958,16 +2265,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="D33">
-        <v>0.012</v>
+        <v>0.5</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1981,19 +2288,19 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C34" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="D34">
-        <v>0.72</v>
+        <v>0.45</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2001,13 +2308,13 @@
         <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D35">
-        <v>0.78</v>
+        <v>0.18</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2021,13 +2328,13 @@
         <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C36" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="D36">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2041,13 +2348,13 @@
         <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="D37">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2061,13 +2368,13 @@
         <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="C38" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D38">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2078,16 +2385,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C39" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D39">
-        <v>0.02</v>
+        <v>0.32</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2098,16 +2405,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C40" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D40">
-        <v>0.015</v>
+        <v>0.58</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2118,16 +2425,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B41" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D41">
-        <v>0.7</v>
+        <v>0.24</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2138,16 +2445,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C42" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="D42">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2158,16 +2465,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C43" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="D43">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2178,16 +2485,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B44" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C44" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D44">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2198,16 +2505,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D45">
-        <v>0.025</v>
+        <v>0.28</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2218,16 +2525,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B46" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C46" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="D46">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2238,16 +2545,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C47" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D47">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2258,16 +2565,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="C48" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D48">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2278,16 +2585,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B49" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C49" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D49">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2298,16 +2605,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B50" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="C50" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D50">
-        <v>0.1</v>
+        <v>0.012</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2318,16 +2625,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C51" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="D51">
-        <v>0.58</v>
+        <v>0.24</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2338,36 +2645,36 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C52" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D52">
-        <v>0.38</v>
+        <v>0.72</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C53" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D53">
-        <v>0.25</v>
+        <v>0.78</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2378,16 +2685,16 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C54" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D54">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2398,16 +2705,16 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B55" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="C55" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D55">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2418,16 +2725,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B56" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C56" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D56">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2438,16 +2745,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="C57" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D57">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2458,16 +2765,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B58" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D58">
-        <v>0.1</v>
+        <v>0.015</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2478,16 +2785,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C59" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D59">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2498,16 +2805,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C60" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D60">
-        <v>0.14</v>
+        <v>0.7</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2518,16 +2825,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B61" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C61" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D61">
-        <v>0.055</v>
+        <v>0.6</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2538,16 +2845,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B62" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C62" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D62">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2558,16 +2865,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B63" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C63" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D63">
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2578,16 +2885,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B64" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="C64" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="D64">
-        <v>0.25</v>
+        <v>0.025</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2598,16 +2905,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B65" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C65" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D65">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2618,16 +2925,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B66" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C66" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D66">
-        <v>0.02</v>
+        <v>0.8</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2638,16 +2945,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B67" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C67" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D67">
-        <v>0.75</v>
+        <v>0.48</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2658,16 +2965,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B68" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C68" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D68">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2678,16 +2985,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B69" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="C69" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="D69">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2698,16 +3005,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="C70" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="D70">
-        <v>0.025</v>
+        <v>0.1</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2718,16 +3025,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B71" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C71" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="D71">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2738,16 +3045,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B72" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C72" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D72">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2758,16 +3065,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B73" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C73" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D73">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2778,16 +3085,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B74" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C74" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D74">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2798,16 +3105,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B75" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C75" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="D75">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2818,16 +3125,16 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B76" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C76" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="D76">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2838,16 +3145,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B77" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C77" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="D77">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2858,16 +3165,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C78" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D78">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2878,16 +3185,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B79" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C79" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D79">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2898,21 +3205,541 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="C80" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="D80">
+        <v>0.1</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>122</v>
+      </c>
+      <c r="B81" t="s">
+        <v>174</v>
+      </c>
+      <c r="C81" t="s">
+        <v>175</v>
+      </c>
+      <c r="D81">
+        <v>0.22</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>122</v>
+      </c>
+      <c r="B82" t="s">
+        <v>176</v>
+      </c>
+      <c r="C82" t="s">
+        <v>177</v>
+      </c>
+      <c r="D82">
+        <v>0.14</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>122</v>
+      </c>
+      <c r="B83" t="s">
+        <v>172</v>
+      </c>
+      <c r="C83" t="s">
+        <v>173</v>
+      </c>
+      <c r="D83">
+        <v>0.055</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>127</v>
+      </c>
+      <c r="B84" t="s">
+        <v>162</v>
+      </c>
+      <c r="C84" t="s">
+        <v>163</v>
+      </c>
+      <c r="D84">
+        <v>0.16</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>127</v>
+      </c>
+      <c r="B85" t="s">
+        <v>180</v>
+      </c>
+      <c r="C85" t="s">
+        <v>181</v>
+      </c>
+      <c r="D85">
+        <v>0.7</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>127</v>
+      </c>
+      <c r="B86" t="s">
+        <v>174</v>
+      </c>
+      <c r="C86" t="s">
+        <v>175</v>
+      </c>
+      <c r="D86">
+        <v>0.45</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>127</v>
+      </c>
+      <c r="B87" t="s">
+        <v>168</v>
+      </c>
+      <c r="C87" t="s">
+        <v>169</v>
+      </c>
+      <c r="D87">
+        <v>0.25</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>127</v>
+      </c>
+      <c r="B88" t="s">
+        <v>170</v>
+      </c>
+      <c r="C88" t="s">
+        <v>171</v>
+      </c>
+      <c r="D88">
+        <v>0.12</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>127</v>
+      </c>
+      <c r="B89" t="s">
+        <v>172</v>
+      </c>
+      <c r="C89" t="s">
+        <v>173</v>
+      </c>
+      <c r="D89">
+        <v>0.02</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>134</v>
+      </c>
+      <c r="B90" t="s">
+        <v>162</v>
+      </c>
+      <c r="C90" t="s">
+        <v>163</v>
+      </c>
+      <c r="D90">
+        <v>0.15</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>134</v>
+      </c>
+      <c r="B91" t="s">
+        <v>180</v>
+      </c>
+      <c r="C91" t="s">
+        <v>181</v>
+      </c>
+      <c r="D91">
+        <v>0.75</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>134</v>
+      </c>
+      <c r="B92" t="s">
+        <v>174</v>
+      </c>
+      <c r="C92" t="s">
+        <v>175</v>
+      </c>
+      <c r="D92">
+        <v>0.52</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>134</v>
+      </c>
+      <c r="B93" t="s">
+        <v>168</v>
+      </c>
+      <c r="C93" t="s">
+        <v>169</v>
+      </c>
+      <c r="D93">
+        <v>0.18</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>134</v>
+      </c>
+      <c r="B94" t="s">
+        <v>172</v>
+      </c>
+      <c r="C94" t="s">
+        <v>173</v>
+      </c>
+      <c r="D94">
+        <v>0.025</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>139</v>
+      </c>
+      <c r="B95" t="s">
+        <v>162</v>
+      </c>
+      <c r="C95" t="s">
+        <v>163</v>
+      </c>
+      <c r="D95">
+        <v>0.14</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>139</v>
+      </c>
+      <c r="B96" t="s">
+        <v>172</v>
+      </c>
+      <c r="C96" t="s">
+        <v>173</v>
+      </c>
+      <c r="D96">
+        <v>0.12</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>139</v>
+      </c>
+      <c r="B97" t="s">
+        <v>178</v>
+      </c>
+      <c r="C97" t="s">
+        <v>179</v>
+      </c>
+      <c r="D97">
+        <v>0.1</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>139</v>
+      </c>
+      <c r="B98" t="s">
+        <v>174</v>
+      </c>
+      <c r="C98" t="s">
+        <v>175</v>
+      </c>
+      <c r="D98">
+        <v>0.2</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>139</v>
+      </c>
+      <c r="B99" t="s">
+        <v>180</v>
+      </c>
+      <c r="C99" t="s">
+        <v>181</v>
+      </c>
+      <c r="D99">
+        <v>0.18</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>139</v>
+      </c>
+      <c r="B100" t="s">
+        <v>176</v>
+      </c>
+      <c r="C100" t="s">
+        <v>177</v>
+      </c>
+      <c r="D100">
+        <v>0.08</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>146</v>
+      </c>
+      <c r="B101" t="s">
+        <v>162</v>
+      </c>
+      <c r="C101" t="s">
+        <v>163</v>
+      </c>
+      <c r="D101">
+        <v>0.12</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>146</v>
+      </c>
+      <c r="B102" t="s">
+        <v>172</v>
+      </c>
+      <c r="C102" t="s">
+        <v>173</v>
+      </c>
+      <c r="D102">
+        <v>0.14</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>146</v>
+      </c>
+      <c r="B103" t="s">
+        <v>178</v>
+      </c>
+      <c r="C103" t="s">
+        <v>179</v>
+      </c>
+      <c r="D103">
+        <v>0.12</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>146</v>
+      </c>
+      <c r="B104" t="s">
+        <v>174</v>
+      </c>
+      <c r="C104" t="s">
+        <v>175</v>
+      </c>
+      <c r="D104">
+        <v>0.16</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>146</v>
+      </c>
+      <c r="B105" t="s">
+        <v>180</v>
+      </c>
+      <c r="C105" t="s">
+        <v>181</v>
+      </c>
+      <c r="D105">
+        <v>0.14</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>146</v>
+      </c>
+      <c r="B106" t="s">
+        <v>176</v>
+      </c>
+      <c r="C106" t="s">
+        <v>177</v>
+      </c>
+      <c r="D106">
         <v>0.06</v>
       </c>
-      <c r="E80">
-        <v>0</v>
-      </c>
-      <c r="F80">
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excel/scavenge.xlsx
+++ b/Assets/Excel/scavenge.xlsx
@@ -1,16 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="21525" windowHeight="12270" activeTab="2"/>
+  </bookViews>
   <sheets>
-    <sheet name="works" sheetId="1" r:id="rId2"/>
-    <sheet name="actions" sheetId="2" r:id="rId3"/>
-    <sheet name="loot" sheetId="3" r:id="rId4"/>
+    <sheet name="works" sheetId="1" r:id="rId1"/>
+    <sheet name="actions" sheetId="2" r:id="rId2"/>
+    <sheet name="loot" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="167">
   <si>
     <t>工作ID</t>
   </si>
@@ -114,7 +133,7 @@
     <t>详情文案(右侧)</t>
   </si>
   <si>
-    <t>缩略图颜色</t>
+    <t>缩略图(空=动作ID)</t>
   </si>
   <si>
     <t>消耗道具ID</t>
@@ -159,7 +178,7 @@
     <t>description</t>
   </si>
   <si>
-    <t>thumbColor</t>
+    <t>thumbImage</t>
   </si>
   <si>
     <t>costItemId</t>
@@ -210,9 +229,6 @@
     <t>二狗家院子角落堆着破筐和破布，他家狗叫得凶，得手快。</t>
   </si>
   <si>
-    <t>#324838</t>
-  </si>
-  <si>
     <t>scavenge_gate_woodshed</t>
   </si>
   <si>
@@ -225,9 +241,6 @@
     <t>村口边上塌了半边的柴房，碎木和旧麻袋最好拣，当心朽木扎手。</t>
   </si>
   <si>
-    <t>#344838</t>
-  </si>
-  <si>
     <t>scavenge_gate_well</t>
   </si>
   <si>
@@ -240,9 +253,6 @@
     <t>井台边湿滑，常能捞到空瓶和洗衣落下的破布，褪色铜币也比别处多一点。</t>
   </si>
   <si>
-    <t>#3A4838</t>
-  </si>
-  <si>
     <t>scavenge_gate_chief</t>
   </si>
   <si>
@@ -255,9 +265,6 @@
     <t>村长家门口管教严，篱笆外仍偶有铜币和空瓶，得赶在村人注意前捡完。</t>
   </si>
   <si>
-    <t>#404838</t>
-  </si>
-  <si>
     <t>scavenge_street_corner</t>
   </si>
   <si>
@@ -288,9 +295,6 @@
     <t>摊贩收摊后留下的破筐和烂菜叶底下，偶尔能翻出铜钉。</t>
   </si>
   <si>
-    <t>#424838</t>
-  </si>
-  <si>
     <t>scavenge_street_alley</t>
   </si>
   <si>
@@ -303,9 +307,6 @@
     <t>店铺后巷阴暗潮湿，碎木和空瓶堆在墙角，得小心碎瓷片。</t>
   </si>
   <si>
-    <t>#384838</t>
-  </si>
-  <si>
     <t>scavenge_barn_heap</t>
   </si>
   <si>
@@ -324,9 +325,6 @@
     <t>谷仓后面堆着村民倒掉的杂物。碎木、破布多，偶尔翻出药草芽。</t>
   </si>
   <si>
-    <t>#504838</t>
-  </si>
-  <si>
     <t>scavenge_barn_shed</t>
   </si>
   <si>
@@ -339,9 +337,6 @@
     <t>棚子底下藏着去年没收干净的麻袋和碎木，药草芽概率略高。</t>
   </si>
   <si>
-    <t>#584838</t>
-  </si>
-  <si>
     <t>scavenge_barn_fence</t>
   </si>
   <si>
@@ -354,9 +349,6 @@
     <t>篱笆被风吹垮了一截，破布和空瓶卡在木刺之间。</t>
   </si>
   <si>
-    <t>#4C4838</t>
-  </si>
-  <si>
     <t>scavenge_stream_shallow</t>
   </si>
   <si>
@@ -375,9 +367,6 @@
     <t>萤溪涨水会把上游的东西冲下来。空瓶、护符比陆地好捞。</t>
   </si>
   <si>
-    <t>#2E5850</t>
-  </si>
-  <si>
     <t>scavenge_stream_eddies</t>
   </si>
   <si>
@@ -390,9 +379,6 @@
     <t>回水湾里打着旋的杂物多，护符和星尘碎屑比浅水区更常见。</t>
   </si>
   <si>
-    <t>#365850</t>
-  </si>
-  <si>
     <t>scavenge_forge_slag</t>
   </si>
   <si>
@@ -411,9 +397,6 @@
     <t>铁匠铺后巷，炉渣和废钉随地都是。想攒锻造料，这里是捷径。</t>
   </si>
   <si>
-    <t>#484038</t>
-  </si>
-  <si>
     <t>scavenge_forge_scrap</t>
   </si>
   <si>
@@ -426,9 +409,6 @@
     <t>张铁匠铺后门外的废铁筐，炉渣和铜钉尤其多。</t>
   </si>
   <si>
-    <t>#504038</t>
-  </si>
-  <si>
     <t>scavenge_monument_base</t>
   </si>
   <si>
@@ -447,9 +427,6 @@
     <t>当年坠星留下的碑旁，泥土里仍嵌着微光颗粒。慢，但星尘碎屑概率最高。</t>
   </si>
   <si>
-    <t>#585040</t>
-  </si>
-  <si>
     <t>scavenge_monument_field</t>
   </si>
   <si>
@@ -462,9 +439,6 @@
     <t>碑外一圈被星尘染色的裸地，耙起来费时，但护符与碎屑都不缺。</t>
   </si>
   <si>
-    <t>#605040</t>
-  </si>
-  <si>
     <t>道具ID</t>
   </si>
   <si>
@@ -516,7 +490,7 @@
     <t>空瓶</t>
   </si>
   <si>
-    <t>splinter</t>
+    <t>wood_scraps</t>
   </si>
   <si>
     <t>碎木</t>
@@ -560,10 +534,1158 @@
 </sst>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -595,7 +1717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -627,7 +1749,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -660,13 +1782,18 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -716,7 +1843,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -766,7 +1893,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -798,7 +1925,7 @@
         <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s">
         <v>61</v>
@@ -816,7 +1943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -848,7 +1975,7 @@
         <v>65</v>
       </c>
       <c r="K4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L4" t="s">
         <v>61</v>
@@ -866,9 +1993,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -880,10 +2007,10 @@
         <v>57</v>
       </c>
       <c r="E5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" t="s">
         <v>68</v>
-      </c>
-      <c r="F5" t="s">
-        <v>69</v>
       </c>
       <c r="G5">
         <v>3.8</v>
@@ -895,10 +2022,10 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L5" t="s">
         <v>61</v>
@@ -916,9 +2043,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -930,10 +2057,10 @@
         <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G6">
         <v>4</v>
@@ -945,10 +2072,10 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="L6" t="s">
         <v>61</v>
@@ -966,9 +2093,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -980,10 +2107,10 @@
         <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G7">
         <v>4.5</v>
@@ -995,10 +2122,10 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K7" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="L7" t="s">
         <v>61</v>
@@ -1016,24 +2143,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -1045,10 +2172,10 @@
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L8" t="s">
         <v>61</v>
@@ -1066,24 +2193,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G9">
         <v>4.5</v>
@@ -1095,10 +2222,10 @@
         <v>2</v>
       </c>
       <c r="J9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K9" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="L9" t="s">
         <v>61</v>
@@ -1116,24 +2243,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1145,10 +2272,10 @@
         <v>2</v>
       </c>
       <c r="J10" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K10" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="L10" t="s">
         <v>61</v>
@@ -1166,24 +2293,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F11" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -1195,10 +2322,10 @@
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="K11" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="L11" t="s">
         <v>61</v>
@@ -1216,24 +2343,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
       </c>
       <c r="C12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" t="s">
         <v>99</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>100</v>
-      </c>
-      <c r="E12" t="s">
-        <v>106</v>
-      </c>
-      <c r="F12" t="s">
-        <v>107</v>
       </c>
       <c r="G12">
         <v>5.5</v>
@@ -1245,10 +2372,10 @@
         <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="K12" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="L12" t="s">
         <v>61</v>
@@ -1266,24 +2393,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1295,10 +2422,10 @@
         <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="K13" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="L13" t="s">
         <v>61</v>
@@ -1316,24 +2443,24 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G14">
         <v>7</v>
@@ -1345,10 +2472,10 @@
         <v>6</v>
       </c>
       <c r="J14" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="K14" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s">
         <v>61</v>
@@ -1366,24 +2493,24 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="F15" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -1395,10 +2522,10 @@
         <v>6</v>
       </c>
       <c r="J15" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="K15" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="L15" t="s">
         <v>61</v>
@@ -1416,24 +2543,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F16" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="G16">
         <v>6</v>
@@ -1445,10 +2572,10 @@
         <v>9</v>
       </c>
       <c r="J16" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="K16" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="L16" t="s">
         <v>61</v>
@@ -1466,24 +2593,24 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F17" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="G17">
         <v>6.5</v>
@@ -1495,10 +2622,10 @@
         <v>9</v>
       </c>
       <c r="J17" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="K17" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="L17" t="s">
         <v>61</v>
@@ -1516,24 +2643,24 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="F18" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="G18">
         <v>9</v>
@@ -1545,10 +2672,10 @@
         <v>12</v>
       </c>
       <c r="J18" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="K18" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="L18" t="s">
         <v>61</v>
@@ -1566,24 +2693,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E19" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F19" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="G19">
         <v>10</v>
@@ -1595,10 +2722,10 @@
         <v>12</v>
       </c>
       <c r="J19" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="K19" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="L19" t="s">
         <v>61</v>
@@ -1617,61 +2744,66 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F106"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D1" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E1" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="F1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="F2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D3">
         <v>0.38</v>
@@ -1683,15 +2815,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D4">
         <v>0.88</v>
@@ -1703,15 +2835,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C5" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D5">
         <v>0.42</v>
@@ -1723,15 +2855,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D6">
         <v>0.3</v>
@@ -1743,15 +2875,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D7">
         <v>0.08</v>
@@ -1763,15 +2895,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D8">
         <v>0.005</v>
@@ -1783,15 +2915,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C9" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D9">
         <v>0.4</v>
@@ -1803,15 +2935,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D10">
         <v>0.92</v>
@@ -1823,15 +2955,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D11">
         <v>0.55</v>
@@ -1843,15 +2975,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D12">
         <v>0.28</v>
@@ -1863,15 +2995,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C13" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D13">
         <v>0.06</v>
@@ -1883,15 +3015,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C14" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D14">
         <v>0.42</v>
@@ -1903,15 +3035,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D15">
         <v>0.85</v>
@@ -1923,15 +3055,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D16">
         <v>0.68</v>
@@ -1943,15 +3075,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C17" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D17">
         <v>0.2</v>
@@ -1963,15 +3095,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C18" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D18">
         <v>0.05</v>
@@ -1983,15 +3115,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C19" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D19">
         <v>0.36</v>
@@ -2003,15 +3135,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C20" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D20">
         <v>0.62</v>
@@ -2023,15 +3155,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D21">
         <v>0.7</v>
@@ -2043,15 +3175,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D22">
         <v>0.14</v>
@@ -2063,15 +3195,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D23">
         <v>0.22</v>
@@ -2083,15 +3215,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D24">
         <v>0.008</v>
@@ -2103,15 +3235,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D25">
         <v>0.35</v>
@@ -2123,15 +3255,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C26" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D26">
         <v>0.5</v>
@@ -2143,15 +3275,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C27" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D27">
         <v>0.55</v>
@@ -2163,15 +3295,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C28" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D28">
         <v>0.18</v>
@@ -2183,15 +3315,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C29" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D29">
         <v>0.25</v>
@@ -2203,15 +3335,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C30" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D30">
         <v>0.006</v>
@@ -2223,15 +3355,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C31" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D31">
         <v>0.3</v>
@@ -2243,15 +3375,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C32" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D32">
         <v>0.65</v>
@@ -2263,15 +3395,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D33">
         <v>0.5</v>
@@ -2283,15 +3415,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D34">
         <v>0.45</v>
@@ -2303,15 +3435,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C35" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D35">
         <v>0.18</v>
@@ -2323,15 +3455,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C36" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D36">
         <v>0.22</v>
@@ -2343,15 +3475,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D37">
         <v>0.05</v>
@@ -2363,15 +3495,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D38">
         <v>0.01</v>
@@ -2383,15 +3515,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C39" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D39">
         <v>0.32</v>
@@ -2403,15 +3535,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C40" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D40">
         <v>0.58</v>
@@ -2423,15 +3555,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C41" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D41">
         <v>0.24</v>
@@ -2443,15 +3575,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B42" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D42">
         <v>0.46</v>
@@ -2463,15 +3595,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B43" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C43" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D43">
         <v>0.08</v>
@@ -2483,15 +3615,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B44" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D44">
         <v>0.18</v>
@@ -2503,15 +3635,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B45" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D45">
         <v>0.28</v>
@@ -2523,15 +3655,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B46" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C46" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D46">
         <v>0.68</v>
@@ -2543,15 +3675,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B47" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C47" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D47">
         <v>0.52</v>
@@ -2563,15 +3695,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C48" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D48">
         <v>0.16</v>
@@ -2583,15 +3715,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B49" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D49">
         <v>0.2</v>
@@ -2603,15 +3735,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D50">
         <v>0.012</v>
@@ -2623,15 +3755,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B51" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D51">
         <v>0.24</v>
@@ -2643,15 +3775,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B52" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C52" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D52">
         <v>0.72</v>
@@ -2663,15 +3795,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C53" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D53">
         <v>0.78</v>
@@ -2683,15 +3815,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B54" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C54" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D54">
         <v>0.4</v>
@@ -2703,15 +3835,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B55" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C55" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D55">
         <v>0.15</v>
@@ -2723,15 +3855,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B56" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C56" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D56">
         <v>0.14</v>
@@ -2743,15 +3875,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C57" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D57">
         <v>0.02</v>
@@ -2763,15 +3895,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B58" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C58" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D58">
         <v>0.015</v>
@@ -2783,15 +3915,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B59" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C59" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D59">
         <v>0.26</v>
@@ -2803,15 +3935,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B60" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D60">
         <v>0.7</v>
@@ -2823,15 +3955,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B61" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C61" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D61">
         <v>0.6</v>
@@ -2843,15 +3975,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B62" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D62">
         <v>0.2</v>
@@ -2863,15 +3995,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B63" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C63" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D63">
         <v>0.12</v>
@@ -2883,15 +4015,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B64" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C64" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D64">
         <v>0.025</v>
@@ -2903,15 +4035,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C65" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D65">
         <v>0.22</v>
@@ -2923,15 +4055,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B66" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C66" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="D66">
         <v>0.8</v>
@@ -2943,15 +4075,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C67" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D67">
         <v>0.48</v>
@@ -2963,15 +4095,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B68" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C68" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D68">
         <v>0.5</v>
@@ -2983,15 +4115,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B69" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C69" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D69">
         <v>0.1</v>
@@ -3003,15 +4135,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C70" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D70">
         <v>0.1</v>
@@ -3023,15 +4155,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C71" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D71">
         <v>0.2</v>
@@ -3043,15 +4175,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B72" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C72" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D72">
         <v>0.58</v>
@@ -3063,15 +4195,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B73" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D73">
         <v>0.38</v>
@@ -3083,15 +4215,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B74" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C74" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D74">
         <v>0.25</v>
@@ -3103,15 +4235,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B75" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C75" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D75">
         <v>0.16</v>
@@ -3123,15 +4255,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B76" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C76" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D76">
         <v>0.06</v>
@@ -3143,15 +4275,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C77" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D77">
         <v>0.04</v>
@@ -3163,15 +4295,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B78" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C78" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D78">
         <v>0.18</v>
@@ -3183,15 +4315,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C79" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="D79">
         <v>0.5</v>
@@ -3203,15 +4335,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C80" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D80">
         <v>0.1</v>
@@ -3223,15 +4355,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B81" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C81" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D81">
         <v>0.22</v>
@@ -3243,15 +4375,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C82" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D82">
         <v>0.14</v>
@@ -3263,15 +4395,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C83" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D83">
         <v>0.055</v>
@@ -3283,15 +4415,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B84" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C84" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D84">
         <v>0.16</v>
@@ -3303,15 +4435,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C85" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D85">
         <v>0.7</v>
@@ -3323,15 +4455,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B86" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C86" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D86">
         <v>0.45</v>
@@ -3343,15 +4475,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B87" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C87" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D87">
         <v>0.25</v>
@@ -3363,15 +4495,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B88" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C88" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="D88">
         <v>0.12</v>
@@ -3383,15 +4515,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B89" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C89" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D89">
         <v>0.02</v>
@@ -3403,15 +4535,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B90" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C90" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D90">
         <v>0.15</v>
@@ -3423,15 +4555,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B91" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C91" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D91">
         <v>0.75</v>
@@ -3443,15 +4575,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B92" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C92" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D92">
         <v>0.52</v>
@@ -3463,15 +4595,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B93" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C93" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D93">
         <v>0.18</v>
@@ -3483,15 +4615,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B94" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C94" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D94">
         <v>0.025</v>
@@ -3503,15 +4635,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B95" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C95" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D95">
         <v>0.14</v>
@@ -3523,15 +4655,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B96" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C96" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D96">
         <v>0.12</v>
@@ -3543,15 +4675,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B97" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C97" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D97">
         <v>0.1</v>
@@ -3563,15 +4695,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B98" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C98" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D98">
         <v>0.2</v>
@@ -3583,15 +4715,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B99" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C99" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D99">
         <v>0.18</v>
@@ -3603,15 +4735,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B100" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C100" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D100">
         <v>0.08</v>
@@ -3623,15 +4755,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B101" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C101" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D101">
         <v>0.12</v>
@@ -3643,15 +4775,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B102" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C102" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="D102">
         <v>0.14</v>
@@ -3663,15 +4795,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B103" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C103" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D103">
         <v>0.12</v>
@@ -3683,15 +4815,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B104" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C104" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="D104">
         <v>0.16</v>
@@ -3703,15 +4835,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B105" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="C105" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D105">
         <v>0.14</v>
@@ -3723,15 +4855,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B106" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C106" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="D106">
         <v>0.06</v>
@@ -3744,5 +4876,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Excel/scavenge.xlsx
+++ b/Assets/Excel/scavenge.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21525" windowHeight="12270" activeTab="2"/>
+    <workbookView windowWidth="21525" windowHeight="12270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="works" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="167">
   <si>
     <t>工作ID</t>
   </si>
@@ -2752,8 +2752,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="23.625" customWidth="1"/>
+    <col min="2" max="2" width="21.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -2897,16 +2901,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C8" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D8">
-        <v>0.005</v>
+        <v>0.4</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -2920,19 +2924,19 @@
         <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D9">
-        <v>0.4</v>
+        <v>0.92</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2940,19 +2944,19 @@
         <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D10">
-        <v>0.92</v>
+        <v>0.55</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2960,13 +2964,13 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D11">
-        <v>0.55</v>
+        <v>0.28</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -2980,13 +2984,13 @@
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D12">
-        <v>0.28</v>
+        <v>0.06</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -2997,16 +3001,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D13">
-        <v>0.06</v>
+        <v>0.42</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -3020,13 +3024,13 @@
         <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C14" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D14">
-        <v>0.42</v>
+        <v>0.85</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -3040,13 +3044,13 @@
         <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C15" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D15">
-        <v>0.85</v>
+        <v>0.68</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -3060,13 +3064,13 @@
         <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C16" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D16">
-        <v>0.68</v>
+        <v>0.2</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -3080,13 +3084,13 @@
         <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C17" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D17">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -3097,16 +3101,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C18" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D18">
-        <v>0.05</v>
+        <v>0.36</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -3120,13 +3124,13 @@
         <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C19" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D19">
-        <v>0.36</v>
+        <v>0.62</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -3140,13 +3144,13 @@
         <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D20">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -3160,13 +3164,13 @@
         <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D21">
-        <v>0.7</v>
+        <v>0.14</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -3180,13 +3184,13 @@
         <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D22">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -3200,13 +3204,13 @@
         <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C23" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D23">
-        <v>0.22</v>
+        <v>0.008</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -3217,16 +3221,16 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C24" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D24">
-        <v>0.008</v>
+        <v>0.35</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -3240,13 +3244,13 @@
         <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D25">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -3260,13 +3264,13 @@
         <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C26" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D26">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -3280,13 +3284,13 @@
         <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C27" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D27">
-        <v>0.55</v>
+        <v>0.18</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -3300,13 +3304,13 @@
         <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C28" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D28">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -3320,13 +3324,13 @@
         <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C29" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D29">
-        <v>0.25</v>
+        <v>0.006</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -3337,16 +3341,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C30" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D30">
-        <v>0.006</v>
+        <v>0.3</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -3360,13 +3364,13 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D31">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -3380,13 +3384,13 @@
         <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D32">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3400,13 +3404,13 @@
         <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D33">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3420,13 +3424,13 @@
         <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C34" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D34">
-        <v>0.45</v>
+        <v>0.18</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3440,13 +3444,13 @@
         <v>78</v>
       </c>
       <c r="B35" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C35" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D35">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3460,13 +3464,13 @@
         <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C36" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D36">
-        <v>0.22</v>
+        <v>0.05</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3480,13 +3484,13 @@
         <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C37" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D37">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3497,16 +3501,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D38">
-        <v>0.01</v>
+        <v>0.32</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -3520,13 +3524,13 @@
         <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C39" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D39">
-        <v>0.32</v>
+        <v>0.58</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3540,13 +3544,13 @@
         <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C40" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D40">
-        <v>0.58</v>
+        <v>0.24</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3560,13 +3564,13 @@
         <v>84</v>
       </c>
       <c r="B41" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C41" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D41">
-        <v>0.24</v>
+        <v>0.46</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3580,13 +3584,13 @@
         <v>84</v>
       </c>
       <c r="B42" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D42">
-        <v>0.46</v>
+        <v>0.08</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3600,13 +3604,13 @@
         <v>84</v>
       </c>
       <c r="B43" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D43">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3617,16 +3621,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B44" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C44" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D44">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3640,13 +3644,13 @@
         <v>88</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D45">
-        <v>0.28</v>
+        <v>0.68</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3660,13 +3664,13 @@
         <v>88</v>
       </c>
       <c r="B46" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C46" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D46">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3680,13 +3684,13 @@
         <v>88</v>
       </c>
       <c r="B47" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C47" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D47">
-        <v>0.52</v>
+        <v>0.16</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3700,13 +3704,13 @@
         <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C48" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D48">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3720,13 +3724,13 @@
         <v>88</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D49">
-        <v>0.2</v>
+        <v>0.012</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3737,16 +3741,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B50" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D50">
-        <v>0.012</v>
+        <v>0.24</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3760,19 +3764,19 @@
         <v>92</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D51">
-        <v>0.24</v>
+        <v>0.72</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -3780,19 +3784,19 @@
         <v>92</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C52" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D52">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -3800,13 +3804,13 @@
         <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C53" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D53">
-        <v>0.78</v>
+        <v>0.4</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3820,13 +3824,13 @@
         <v>92</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C54" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D54">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3840,13 +3844,13 @@
         <v>92</v>
       </c>
       <c r="B55" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C55" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D55">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3860,13 +3864,13 @@
         <v>92</v>
       </c>
       <c r="B56" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C56" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D56">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3880,13 +3884,13 @@
         <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C57" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D57">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3897,16 +3901,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B58" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C58" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D58">
-        <v>0.015</v>
+        <v>0.26</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -3920,13 +3924,13 @@
         <v>98</v>
       </c>
       <c r="B59" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C59" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D59">
-        <v>0.26</v>
+        <v>0.7</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3940,13 +3944,13 @@
         <v>98</v>
       </c>
       <c r="B60" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C60" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D60">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3960,13 +3964,13 @@
         <v>98</v>
       </c>
       <c r="B61" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="D61">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3980,13 +3984,13 @@
         <v>98</v>
       </c>
       <c r="B62" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C62" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D62">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -4000,13 +4004,13 @@
         <v>98</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C63" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D63">
-        <v>0.12</v>
+        <v>0.025</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4017,16 +4021,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="C64" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="D64">
-        <v>0.025</v>
+        <v>0.22</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4040,13 +4044,13 @@
         <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C65" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D65">
-        <v>0.22</v>
+        <v>0.8</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4060,13 +4064,13 @@
         <v>102</v>
       </c>
       <c r="B66" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C66" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D66">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4080,13 +4084,13 @@
         <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C67" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D67">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4100,13 +4104,13 @@
         <v>102</v>
       </c>
       <c r="B68" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C68" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D68">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4120,10 +4124,10 @@
         <v>102</v>
       </c>
       <c r="B69" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D69">
         <v>0.1</v>
@@ -4137,16 +4141,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B70" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C70" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D70">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4160,13 +4164,13 @@
         <v>106</v>
       </c>
       <c r="B71" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C71" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D71">
-        <v>0.2</v>
+        <v>0.58</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4180,13 +4184,13 @@
         <v>106</v>
       </c>
       <c r="B72" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C72" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D72">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4200,13 +4204,13 @@
         <v>106</v>
       </c>
       <c r="B73" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C73" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D73">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4220,13 +4224,13 @@
         <v>106</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C74" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D74">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4240,13 +4244,13 @@
         <v>106</v>
       </c>
       <c r="B75" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C75" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D75">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4260,13 +4264,13 @@
         <v>106</v>
       </c>
       <c r="B76" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C76" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D76">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4277,16 +4281,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B77" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C77" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D77">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -4300,13 +4304,13 @@
         <v>112</v>
       </c>
       <c r="B78" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C78" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D78">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -4320,13 +4324,13 @@
         <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C79" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D79">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -4340,13 +4344,13 @@
         <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C80" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D80">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -4360,13 +4364,13 @@
         <v>112</v>
       </c>
       <c r="B81" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C81" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D81">
-        <v>0.22</v>
+        <v>0.14</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -4380,13 +4384,13 @@
         <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C82" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D82">
-        <v>0.14</v>
+        <v>0.055</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -4397,16 +4401,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B83" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C83" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D83">
-        <v>0.055</v>
+        <v>0.16</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -4420,13 +4424,13 @@
         <v>116</v>
       </c>
       <c r="B84" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C84" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D84">
-        <v>0.16</v>
+        <v>0.7</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -4440,13 +4444,13 @@
         <v>116</v>
       </c>
       <c r="B85" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C85" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D85">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -4460,13 +4464,13 @@
         <v>116</v>
       </c>
       <c r="B86" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C86" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D86">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4480,13 +4484,13 @@
         <v>116</v>
       </c>
       <c r="B87" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C87" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D87">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -4500,13 +4504,13 @@
         <v>116</v>
       </c>
       <c r="B88" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C88" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D88">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -4517,16 +4521,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B89" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C89" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D89">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -4540,13 +4544,13 @@
         <v>122</v>
       </c>
       <c r="B90" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C90" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D90">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -4560,13 +4564,13 @@
         <v>122</v>
       </c>
       <c r="B91" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C91" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D91">
-        <v>0.75</v>
+        <v>0.52</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -4580,13 +4584,13 @@
         <v>122</v>
       </c>
       <c r="B92" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C92" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D92">
-        <v>0.52</v>
+        <v>0.18</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -4600,13 +4604,13 @@
         <v>122</v>
       </c>
       <c r="B93" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C93" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D93">
-        <v>0.18</v>
+        <v>0.025</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -4617,16 +4621,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B94" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C94" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D94">
-        <v>0.025</v>
+        <v>0.14</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -4640,13 +4644,13 @@
         <v>126</v>
       </c>
       <c r="B95" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C95" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D95">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -4660,13 +4664,13 @@
         <v>126</v>
       </c>
       <c r="B96" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C96" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D96">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -4680,13 +4684,13 @@
         <v>126</v>
       </c>
       <c r="B97" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C97" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D97">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -4700,13 +4704,13 @@
         <v>126</v>
       </c>
       <c r="B98" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C98" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D98">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -4720,13 +4724,13 @@
         <v>126</v>
       </c>
       <c r="B99" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C99" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D99">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -4737,16 +4741,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B100" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="C100" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="D100">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -4760,13 +4764,13 @@
         <v>132</v>
       </c>
       <c r="B101" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C101" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D101">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -4780,13 +4784,13 @@
         <v>132</v>
       </c>
       <c r="B102" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C102" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D102">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -4800,13 +4804,13 @@
         <v>132</v>
       </c>
       <c r="B103" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C103" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D103">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4820,13 +4824,13 @@
         <v>132</v>
       </c>
       <c r="B104" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C104" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D104">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4840,38 +4844,18 @@
         <v>132</v>
       </c>
       <c r="B105" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C105" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D105">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="E105">
         <v>0</v>
       </c>
       <c r="F105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106" t="s">
-        <v>132</v>
-      </c>
-      <c r="B106" t="s">
-        <v>161</v>
-      </c>
-      <c r="C106" t="s">
-        <v>162</v>
-      </c>
-      <c r="D106">
-        <v>0.06</v>
-      </c>
-      <c r="E106">
-        <v>0</v>
-      </c>
-      <c r="F106">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excel/scavenge.xlsx
+++ b/Assets/Excel/scavenge.xlsx
@@ -1,35 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="21525" windowHeight="12270" activeTab="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="works" sheetId="1" r:id="rId1"/>
-    <sheet name="actions" sheetId="2" r:id="rId2"/>
-    <sheet name="loot" sheetId="3" r:id="rId3"/>
+    <sheet name="works" sheetId="1" r:id="rId2"/>
+    <sheet name="actions" sheetId="2" r:id="rId3"/>
+    <sheet name="loot" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
   <si>
     <t>工作ID</t>
   </si>
@@ -493,7 +474,7 @@
     <t>wood_scraps</t>
   </si>
   <si>
-    <t>碎木</t>
+    <t>木头废料</t>
   </si>
   <si>
     <t>worn_coin</t>
@@ -511,7 +492,7 @@
     <t>copper_nail</t>
   </si>
   <si>
-    <t>铜钉</t>
+    <t>锈钉子</t>
   </si>
   <si>
     <t>herb_sprout</t>
@@ -534,1158 +515,10 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="33">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="9">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-  </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Traditional Arabic"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Traditional Arabic"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1717,7 +550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1749,7 +582,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1782,18 +615,13 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -1843,7 +671,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1893,7 +721,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -1943,7 +771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -1993,7 +821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -2019,7 +847,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="s">
         <v>69</v>
@@ -2043,7 +871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -2069,7 +897,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" t="s">
         <v>73</v>
@@ -2093,7 +921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7">
       <c r="A7" t="s">
         <v>74</v>
       </c>
@@ -2119,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J7" t="s">
         <v>77</v>
@@ -2143,7 +971,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8">
       <c r="A8" t="s">
         <v>78</v>
       </c>
@@ -2169,7 +997,7 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J8" t="s">
         <v>83</v>
@@ -2193,7 +1021,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -2219,7 +1047,7 @@
         <v>9</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J9" t="s">
         <v>87</v>
@@ -2243,7 +1071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10">
       <c r="A10" t="s">
         <v>88</v>
       </c>
@@ -2269,7 +1097,7 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J10" t="s">
         <v>91</v>
@@ -2293,7 +1121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11">
       <c r="A11" t="s">
         <v>92</v>
       </c>
@@ -2319,7 +1147,7 @@
         <v>12</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J11" t="s">
         <v>97</v>
@@ -2343,7 +1171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12">
       <c r="A12" t="s">
         <v>98</v>
       </c>
@@ -2369,7 +1197,7 @@
         <v>13</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J12" t="s">
         <v>101</v>
@@ -2393,7 +1221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13">
       <c r="A13" t="s">
         <v>102</v>
       </c>
@@ -2419,7 +1247,7 @@
         <v>12</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J13" t="s">
         <v>105</v>
@@ -2443,7 +1271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14">
       <c r="A14" t="s">
         <v>106</v>
       </c>
@@ -2469,7 +1297,7 @@
         <v>16</v>
       </c>
       <c r="I14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J14" t="s">
         <v>111</v>
@@ -2493,7 +1321,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15">
       <c r="A15" t="s">
         <v>112</v>
       </c>
@@ -2519,7 +1347,7 @@
         <v>18</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J15" t="s">
         <v>115</v>
@@ -2543,7 +1371,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16">
       <c r="A16" t="s">
         <v>116</v>
       </c>
@@ -2569,7 +1397,7 @@
         <v>18</v>
       </c>
       <c r="I16">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J16" t="s">
         <v>121</v>
@@ -2593,7 +1421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17">
       <c r="A17" t="s">
         <v>122</v>
       </c>
@@ -2619,7 +1447,7 @@
         <v>19</v>
       </c>
       <c r="I17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J17" t="s">
         <v>125</v>
@@ -2643,7 +1471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18">
       <c r="A18" t="s">
         <v>126</v>
       </c>
@@ -2669,7 +1497,7 @@
         <v>24</v>
       </c>
       <c r="I18">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J18" t="s">
         <v>131</v>
@@ -2693,7 +1521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19">
       <c r="A19" t="s">
         <v>132</v>
       </c>
@@ -2719,7 +1547,7 @@
         <v>26</v>
       </c>
       <c r="I19">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
         <v>135</v>
@@ -2744,22 +1572,13 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F105"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="1" width="23.625" customWidth="1"/>
-    <col min="2" max="2" width="21.25" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -2779,7 +1598,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2">
       <c r="A2" t="s">
         <v>141</v>
       </c>
@@ -2799,7 +1618,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -2819,7 +1638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -2839,7 +1658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -2859,7 +1678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -2879,7 +1698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -2899,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -2919,7 +1738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9">
       <c r="A9" t="s">
         <v>62</v>
       </c>
@@ -2939,7 +1758,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -2959,7 +1778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -2979,7 +1798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -2999,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -3019,7 +1838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -3039,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -3059,7 +1878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -3079,7 +1898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -3099,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18">
       <c r="A18" t="s">
         <v>70</v>
       </c>
@@ -3119,7 +1938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -3139,7 +1958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -3159,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -3179,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -3199,7 +2018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23">
       <c r="A23" t="s">
         <v>70</v>
       </c>
@@ -3219,7 +2038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -3239,7 +2058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25">
       <c r="A25" t="s">
         <v>74</v>
       </c>
@@ -3259,7 +2078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -3279,7 +2098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27">
       <c r="A27" t="s">
         <v>74</v>
       </c>
@@ -3299,7 +2118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28">
       <c r="A28" t="s">
         <v>74</v>
       </c>
@@ -3319,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -3339,7 +2158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30">
       <c r="A30" t="s">
         <v>78</v>
       </c>
@@ -3359,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -3379,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -3399,7 +2218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -3419,7 +2238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -3439,7 +2258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -3459,7 +2278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -3479,7 +2298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37">
       <c r="A37" t="s">
         <v>78</v>
       </c>
@@ -3499,7 +2318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -3519,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -3539,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40">
       <c r="A40" t="s">
         <v>84</v>
       </c>
@@ -3559,7 +2378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -3579,7 +2398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -3599,7 +2418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -3619,7 +2438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44">
       <c r="A44" t="s">
         <v>88</v>
       </c>
@@ -3639,7 +2458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45">
       <c r="A45" t="s">
         <v>88</v>
       </c>
@@ -3659,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -3679,7 +2498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47">
       <c r="A47" t="s">
         <v>88</v>
       </c>
@@ -3699,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48">
       <c r="A48" t="s">
         <v>88</v>
       </c>
@@ -3719,7 +2538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49">
       <c r="A49" t="s">
         <v>88</v>
       </c>
@@ -3739,7 +2558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50">
       <c r="A50" t="s">
         <v>92</v>
       </c>
@@ -3759,7 +2578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51">
       <c r="A51" t="s">
         <v>92</v>
       </c>
@@ -3779,7 +2598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52">
       <c r="A52" t="s">
         <v>92</v>
       </c>
@@ -3799,7 +2618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53">
       <c r="A53" t="s">
         <v>92</v>
       </c>
@@ -3819,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54">
       <c r="A54" t="s">
         <v>92</v>
       </c>
@@ -3839,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55">
       <c r="A55" t="s">
         <v>92</v>
       </c>
@@ -3859,7 +2678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56">
       <c r="A56" t="s">
         <v>92</v>
       </c>
@@ -3879,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57">
       <c r="A57" t="s">
         <v>92</v>
       </c>
@@ -3899,7 +2718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58">
       <c r="A58" t="s">
         <v>98</v>
       </c>
@@ -3919,7 +2738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59">
       <c r="A59" t="s">
         <v>98</v>
       </c>
@@ -3939,7 +2758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60">
       <c r="A60" t="s">
         <v>98</v>
       </c>
@@ -3959,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61">
       <c r="A61" t="s">
         <v>98</v>
       </c>
@@ -3979,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -3999,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63">
       <c r="A63" t="s">
         <v>98</v>
       </c>
@@ -4019,7 +2838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64">
       <c r="A64" t="s">
         <v>102</v>
       </c>
@@ -4039,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65">
       <c r="A65" t="s">
         <v>102</v>
       </c>
@@ -4059,7 +2878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66">
       <c r="A66" t="s">
         <v>102</v>
       </c>
@@ -4079,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67">
       <c r="A67" t="s">
         <v>102</v>
       </c>
@@ -4099,7 +2918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68">
       <c r="A68" t="s">
         <v>102</v>
       </c>
@@ -4119,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69">
       <c r="A69" t="s">
         <v>102</v>
       </c>
@@ -4139,7 +2958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70">
       <c r="A70" t="s">
         <v>106</v>
       </c>
@@ -4159,7 +2978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71">
       <c r="A71" t="s">
         <v>106</v>
       </c>
@@ -4179,7 +2998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72">
       <c r="A72" t="s">
         <v>106</v>
       </c>
@@ -4199,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73">
       <c r="A73" t="s">
         <v>106</v>
       </c>
@@ -4219,7 +3038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74">
       <c r="A74" t="s">
         <v>106</v>
       </c>
@@ -4239,7 +3058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75">
       <c r="A75" t="s">
         <v>106</v>
       </c>
@@ -4259,7 +3078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76">
       <c r="A76" t="s">
         <v>106</v>
       </c>
@@ -4279,7 +3098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77">
       <c r="A77" t="s">
         <v>112</v>
       </c>
@@ -4299,7 +3118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78">
       <c r="A78" t="s">
         <v>112</v>
       </c>
@@ -4319,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79">
       <c r="A79" t="s">
         <v>112</v>
       </c>
@@ -4339,7 +3158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80">
       <c r="A80" t="s">
         <v>112</v>
       </c>
@@ -4359,7 +3178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81">
       <c r="A81" t="s">
         <v>112</v>
       </c>
@@ -4379,7 +3198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -4399,7 +3218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83">
       <c r="A83" t="s">
         <v>116</v>
       </c>
@@ -4419,7 +3238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84">
       <c r="A84" t="s">
         <v>116</v>
       </c>
@@ -4439,7 +3258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85">
       <c r="A85" t="s">
         <v>116</v>
       </c>
@@ -4459,7 +3278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86">
       <c r="A86" t="s">
         <v>116</v>
       </c>
@@ -4479,7 +3298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87">
       <c r="A87" t="s">
         <v>116</v>
       </c>
@@ -4499,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88">
       <c r="A88" t="s">
         <v>116</v>
       </c>
@@ -4519,7 +3338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89">
       <c r="A89" t="s">
         <v>122</v>
       </c>
@@ -4539,7 +3358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90">
       <c r="A90" t="s">
         <v>122</v>
       </c>
@@ -4559,7 +3378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91">
       <c r="A91" t="s">
         <v>122</v>
       </c>
@@ -4579,7 +3398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92">
       <c r="A92" t="s">
         <v>122</v>
       </c>
@@ -4599,7 +3418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93">
       <c r="A93" t="s">
         <v>122</v>
       </c>
@@ -4619,7 +3438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94">
       <c r="A94" t="s">
         <v>126</v>
       </c>
@@ -4639,7 +3458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95">
       <c r="A95" t="s">
         <v>126</v>
       </c>
@@ -4659,7 +3478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96">
       <c r="A96" t="s">
         <v>126</v>
       </c>
@@ -4679,7 +3498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97">
       <c r="A97" t="s">
         <v>126</v>
       </c>
@@ -4699,7 +3518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -4719,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99">
       <c r="A99" t="s">
         <v>126</v>
       </c>
@@ -4739,7 +3558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100">
       <c r="A100" t="s">
         <v>132</v>
       </c>
@@ -4759,7 +3578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101">
       <c r="A101" t="s">
         <v>132</v>
       </c>
@@ -4779,7 +3598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102">
       <c r="A102" t="s">
         <v>132</v>
       </c>
@@ -4799,7 +3618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103">
       <c r="A103" t="s">
         <v>132</v>
       </c>
@@ -4819,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104">
       <c r="A104" t="s">
         <v>132</v>
       </c>
@@ -4839,7 +3658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105">
       <c r="A105" t="s">
         <v>132</v>
       </c>
@@ -4860,7 +3679,5 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Excel/scavenge.xlsx
+++ b/Assets/Excel/scavenge.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>工作ID</t>
   </si>
@@ -177,15 +177,42 @@
     <t>goldMax</t>
   </si>
   <si>
+    <t>scavenge_gate_ergou</t>
+  </si>
+  <si>
+    <t>gate</t>
+  </si>
+  <si>
+    <t>村口</t>
+  </si>
+  <si>
+    <t>二狗家</t>
+  </si>
+  <si>
+    <t>村口 · 二狗家</t>
+  </si>
+  <si>
+    <t>二狗家院子角落堆着破筐和破布，他家狗叫得凶，得手快。</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>scavenge_gate_woodshed</t>
+  </si>
+  <si>
+    <t>废弃柴房</t>
+  </si>
+  <si>
+    <t>村口 · 废弃柴房</t>
+  </si>
+  <si>
+    <t>村口边上塌了半边的柴房，碎木和旧麻袋最好拣，当心朽木扎手。</t>
+  </si>
+  <si>
     <t>scavenge_gate_fork</t>
   </si>
   <si>
-    <t>gate</t>
-  </si>
-  <si>
-    <t>村口</t>
-  </si>
-  <si>
     <t>村子岔路口</t>
   </si>
   <si>
@@ -195,33 +222,6 @@
     <t>进出村的岔路口总有人掉东西。破布、空瓶最多，适合刚落脚的新手。</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>scavenge_gate_ergou</t>
-  </si>
-  <si>
-    <t>二狗家</t>
-  </si>
-  <si>
-    <t>村口 · 二狗家</t>
-  </si>
-  <si>
-    <t>二狗家院子角落堆着破筐和破布，他家狗叫得凶，得手快。</t>
-  </si>
-  <si>
-    <t>scavenge_gate_woodshed</t>
-  </si>
-  <si>
-    <t>废弃柴房</t>
-  </si>
-  <si>
-    <t>村口 · 废弃柴房</t>
-  </si>
-  <si>
-    <t>村口边上塌了半边的柴房，碎木和旧麻袋最好拣，当心朽木扎手。</t>
-  </si>
-  <si>
     <t>scavenge_gate_well</t>
   </si>
   <si>
@@ -246,178 +246,124 @@
     <t>村长家门口管教严，篱笆外仍偶有铜币和空瓶，得赶在村人注意前捡完。</t>
   </si>
   <si>
-    <t>scavenge_street_corner</t>
-  </si>
-  <si>
-    <t>street</t>
-  </si>
-  <si>
-    <t>街道</t>
-  </si>
-  <si>
-    <t>街角</t>
-  </si>
-  <si>
-    <t>街道 · 街角</t>
-  </si>
-  <si>
-    <t>早市散场后，街角堆着果皮和破筐。铜钉、褪色铜币比村口常见些。</t>
-  </si>
-  <si>
-    <t>scavenge_street_market</t>
-  </si>
-  <si>
-    <t>早市残骸</t>
-  </si>
-  <si>
-    <t>街道 · 早市残骸</t>
-  </si>
-  <si>
-    <t>摊贩收摊后留下的破筐和烂菜叶底下，偶尔能翻出铜钉。</t>
-  </si>
-  <si>
-    <t>scavenge_street_alley</t>
-  </si>
-  <si>
-    <t>后巷</t>
-  </si>
-  <si>
-    <t>街道 · 后巷</t>
-  </si>
-  <si>
-    <t>店铺后巷阴暗潮湿，碎木和空瓶堆在墙角，得小心碎瓷片。</t>
-  </si>
-  <si>
-    <t>scavenge_barn_heap</t>
-  </si>
-  <si>
-    <t>barn</t>
-  </si>
-  <si>
-    <t>谷仓后</t>
-  </si>
-  <si>
-    <t>废料堆</t>
-  </si>
-  <si>
-    <t>谷仓后 · 废料堆</t>
-  </si>
-  <si>
-    <t>谷仓后面堆着村民倒掉的杂物。碎木、破布多，偶尔翻出药草芽。</t>
-  </si>
-  <si>
-    <t>scavenge_barn_shed</t>
-  </si>
-  <si>
-    <t>储物棚</t>
-  </si>
-  <si>
-    <t>谷仓后 · 储物棚</t>
-  </si>
-  <si>
-    <t>棚子底下藏着去年没收干净的麻袋和碎木，药草芽概率略高。</t>
-  </si>
-  <si>
-    <t>scavenge_barn_fence</t>
-  </si>
-  <si>
-    <t>篱笆边</t>
-  </si>
-  <si>
-    <t>谷仓后 · 篱笆边</t>
-  </si>
-  <si>
-    <t>篱笆被风吹垮了一截，破布和空瓶卡在木刺之间。</t>
-  </si>
-  <si>
-    <t>scavenge_stream_shallow</t>
-  </si>
-  <si>
-    <t>stream</t>
-  </si>
-  <si>
-    <t>溪滩</t>
-  </si>
-  <si>
-    <t>浅水区</t>
-  </si>
-  <si>
-    <t>溪滩 · 浅水区</t>
-  </si>
-  <si>
-    <t>萤溪涨水会把上游的东西冲下来。空瓶、护符比陆地好捞。</t>
-  </si>
-  <si>
-    <t>scavenge_stream_eddies</t>
-  </si>
-  <si>
-    <t>回水湾</t>
-  </si>
-  <si>
-    <t>溪滩 · 回水湾</t>
-  </si>
-  <si>
-    <t>回水湾里打着旋的杂物多，护符和星尘碎屑比浅水区更常见。</t>
-  </si>
-  <si>
-    <t>scavenge_forge_slag</t>
-  </si>
-  <si>
-    <t>forge_alley</t>
-  </si>
-  <si>
-    <t>铁砧巷</t>
-  </si>
-  <si>
-    <t>炉渣堆</t>
-  </si>
-  <si>
-    <t>铁砧巷 · 炉渣堆</t>
-  </si>
-  <si>
-    <t>铁匠铺后巷，炉渣和废钉随地都是。想攒锻造料，这里是捷径。</t>
-  </si>
-  <si>
-    <t>scavenge_forge_scrap</t>
-  </si>
-  <si>
-    <t>张铁匠铺后</t>
-  </si>
-  <si>
-    <t>铁砧巷 · 张铁匠铺后</t>
-  </si>
-  <si>
-    <t>张铁匠铺后门外的废铁筐，炉渣和铜钉尤其多。</t>
-  </si>
-  <si>
-    <t>scavenge_monument_base</t>
-  </si>
-  <si>
-    <t>monument</t>
-  </si>
-  <si>
-    <t>坠星碑</t>
-  </si>
-  <si>
-    <t>碑基</t>
-  </si>
-  <si>
-    <t>坠星碑 · 碑基</t>
-  </si>
-  <si>
-    <t>当年坠星留下的碑旁，泥土里仍嵌着微光颗粒。慢，但星尘碎屑概率最高。</t>
-  </si>
-  <si>
-    <t>scavenge_monument_field</t>
-  </si>
-  <si>
-    <t>星屑地</t>
-  </si>
-  <si>
-    <t>坠星碑 · 星屑地</t>
-  </si>
-  <si>
-    <t>碑外一圈被星尘染色的裸地，耙起来费时，但护符与碎屑都不缺。</t>
+    <t>scavenge_black_pine_trail</t>
+  </si>
+  <si>
+    <t>black_pine</t>
+  </si>
+  <si>
+    <t>黑松林</t>
+  </si>
+  <si>
+    <t>林间小道</t>
+  </si>
+  <si>
+    <t>黑松林 · 林间小道</t>
+  </si>
+  <si>
+    <t>村外黑松林入口的小道，落叶底下藏着碎木和药草芽，比村口安静得多。</t>
+  </si>
+  <si>
+    <t>scavenge_black_pine_fallen</t>
+  </si>
+  <si>
+    <t>倒下的老松树</t>
+  </si>
+  <si>
+    <t>黑松林 · 倒下的老松树</t>
+  </si>
+  <si>
+    <t>雷击倒的老松横在路中，树皮剥落处能抠出碎木和旧护符，得提防松脂粘手。</t>
+  </si>
+  <si>
+    <t>scavenge_black_pine_shrine</t>
+  </si>
+  <si>
+    <t>森林神龛</t>
+  </si>
+  <si>
+    <t>黑松林 · 森林神龛</t>
+  </si>
+  <si>
+    <t>林中小神龛前常有人留下供品和旧护符，拾荒时别惊动路过的猎人。</t>
+  </si>
+  <si>
+    <t>scavenge_black_pine_hunter</t>
+  </si>
+  <si>
+    <t>猎人的小屋</t>
+  </si>
+  <si>
+    <t>黑松林 · 猎人的小屋</t>
+  </si>
+  <si>
+    <t>猎人外出时，篱笆外的废筐里偶有铜钉和空瓶，别碰他挂着的兽皮。</t>
+  </si>
+  <si>
+    <t>scavenge_black_pine_stream</t>
+  </si>
+  <si>
+    <t>林间溪流</t>
+  </si>
+  <si>
+    <t>黑松林 · 林间溪流</t>
+  </si>
+  <si>
+    <t>林溪浅滩比村井边更清，空瓶和药草芽常被水冲在岸石上。</t>
+  </si>
+  <si>
+    <t>scavenge_black_pine_bandit</t>
+  </si>
+  <si>
+    <t>盗贼窝</t>
+  </si>
+  <si>
+    <t>黑松林 · 盗贼窝</t>
+  </si>
+  <si>
+    <t>废弃盗匪营地，破布和铜钉堆在熄灭的火堆旁，得手要快，别久留。</t>
+  </si>
+  <si>
+    <t>scavenge_old_road_camp</t>
+  </si>
+  <si>
+    <t>old_road</t>
+  </si>
+  <si>
+    <t>冒险者旧道</t>
+  </si>
+  <si>
+    <t>废弃的营地</t>
+  </si>
+  <si>
+    <t>冒险者旧道 · 废弃的营地</t>
+  </si>
+  <si>
+    <t>旧道上被遗弃的营火圈，破布和褪色铜币混在灰烬里，像是匆匆撤离留下的。</t>
+  </si>
+  <si>
+    <t>scavenge_old_road_station</t>
+  </si>
+  <si>
+    <t>马车驿站</t>
+  </si>
+  <si>
+    <t>冒险者旧道 · 马车驿站</t>
+  </si>
+  <si>
+    <t>停运的驿站月台边，空瓶和铜钉比营地更常见，墙缝里还卡着旧护符。</t>
+  </si>
+  <si>
+    <t>scavenge_old_road_bridge</t>
+  </si>
+  <si>
+    <t>断桥边</t>
+  </si>
+  <si>
+    <t>冒险者旧道 · 断桥边</t>
+  </si>
+  <si>
+    <t>古桥断在河心，桥墩缝里嵌着微光碎屑，冒险者曾在此休整，遗物仍散落在岸坡。</t>
   </si>
   <si>
     <t>道具ID</t>
@@ -465,18 +411,18 @@
     <t>破布</t>
   </si>
   <si>
+    <t>wood_scraps</t>
+  </si>
+  <si>
+    <t>木头废料</t>
+  </si>
+  <si>
     <t>empty_bottle</t>
   </si>
   <si>
     <t>空瓶</t>
   </si>
   <si>
-    <t>wood_scraps</t>
-  </si>
-  <si>
-    <t>木头废料</t>
-  </si>
-  <si>
     <t>worn_coin</t>
   </si>
   <si>
@@ -489,28 +435,22 @@
     <t>星尘碎屑</t>
   </si>
   <si>
+    <t>herb_sprout</t>
+  </si>
+  <si>
+    <t>药草芽</t>
+  </si>
+  <si>
+    <t>old_charm</t>
+  </si>
+  <si>
+    <t>旧护符</t>
+  </si>
+  <si>
     <t>copper_nail</t>
   </si>
   <si>
     <t>锈钉子</t>
-  </si>
-  <si>
-    <t>herb_sprout</t>
-  </si>
-  <si>
-    <t>药草芽</t>
-  </si>
-  <si>
-    <t>old_charm</t>
-  </si>
-  <si>
-    <t>旧护符</t>
-  </si>
-  <si>
-    <t>slag</t>
-  </si>
-  <si>
-    <t>炉渣</t>
   </si>
 </sst>
 </file>
@@ -741,10 +681,10 @@
         <v>59</v>
       </c>
       <c r="G3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -762,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="O3">
         <v>1</v>
@@ -791,13 +731,13 @@
         <v>64</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="s">
         <v>65</v>
@@ -812,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -841,13 +781,13 @@
         <v>68</v>
       </c>
       <c r="G5">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H5">
         <v>6</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="s">
         <v>69</v>
@@ -862,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="O5">
         <v>1</v>
@@ -897,7 +837,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="s">
         <v>73</v>
@@ -947,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="s">
         <v>77</v>
@@ -991,13 +931,13 @@
         <v>82</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
         <v>83</v>
@@ -1012,13 +952,13 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1041,13 +981,13 @@
         <v>86</v>
       </c>
       <c r="G9">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J9" t="s">
         <v>87</v>
@@ -1062,13 +1002,13 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1091,13 +1031,13 @@
         <v>90</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J10" t="s">
         <v>91</v>
@@ -1112,13 +1052,13 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="O10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1129,28 +1069,28 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
         <v>93</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>94</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11">
+        <v>5.5</v>
+      </c>
+      <c r="H11">
+        <v>13</v>
+      </c>
+      <c r="I11">
+        <v>13</v>
+      </c>
+      <c r="J11" t="s">
         <v>95</v>
-      </c>
-      <c r="F11" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-      <c r="H11">
-        <v>12</v>
-      </c>
-      <c r="I11">
-        <v>8</v>
-      </c>
-      <c r="J11" t="s">
-        <v>97</v>
       </c>
       <c r="K11" t="s">
         <v>92</v>
@@ -1168,42 +1108,42 @@
         <v>2</v>
       </c>
       <c r="P11">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12">
+        <v>6.5</v>
+      </c>
+      <c r="H12">
+        <v>15</v>
+      </c>
+      <c r="I12">
+        <v>14</v>
+      </c>
+      <c r="J12" t="s">
         <v>99</v>
       </c>
-      <c r="F12" t="s">
-        <v>100</v>
-      </c>
-      <c r="G12">
-        <v>5.5</v>
-      </c>
-      <c r="H12">
-        <v>13</v>
-      </c>
-      <c r="I12">
-        <v>9</v>
-      </c>
-      <c r="J12" t="s">
-        <v>101</v>
-      </c>
       <c r="K12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L12" t="s">
         <v>61</v>
@@ -1212,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="O12">
         <v>2</v>
@@ -1223,37 +1163,37 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13">
+        <v>7</v>
+      </c>
+      <c r="H13">
+        <v>16</v>
+      </c>
+      <c r="I13">
+        <v>15</v>
+      </c>
+      <c r="J13" t="s">
         <v>103</v>
       </c>
-      <c r="F13" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-      <c r="H13">
-        <v>12</v>
-      </c>
-      <c r="I13">
-        <v>10</v>
-      </c>
-      <c r="J13" t="s">
-        <v>105</v>
-      </c>
       <c r="K13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L13" t="s">
         <v>61</v>
@@ -1262,48 +1202,48 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="O13">
         <v>2</v>
       </c>
       <c r="P13">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
       <c r="C14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" t="s">
         <v>107</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>108</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14">
+        <v>7.5</v>
+      </c>
+      <c r="H14">
+        <v>18</v>
+      </c>
+      <c r="I14">
+        <v>20</v>
+      </c>
+      <c r="J14" t="s">
         <v>109</v>
       </c>
-      <c r="F14" t="s">
-        <v>110</v>
-      </c>
-      <c r="G14">
-        <v>7</v>
-      </c>
-      <c r="H14">
-        <v>16</v>
-      </c>
-      <c r="I14">
-        <v>11</v>
-      </c>
-      <c r="J14" t="s">
-        <v>111</v>
-      </c>
       <c r="K14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L14" t="s">
         <v>61</v>
@@ -1312,48 +1252,48 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="O14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G15">
         <v>8</v>
       </c>
       <c r="H15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I15">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s">
         <v>61</v>
@@ -1362,48 +1302,48 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="O15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
       </c>
       <c r="C16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16">
+        <v>8.5</v>
+      </c>
+      <c r="H16">
+        <v>20</v>
+      </c>
+      <c r="I16">
+        <v>22</v>
+      </c>
+      <c r="J16" t="s">
         <v>117</v>
       </c>
-      <c r="D16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" t="s">
-        <v>119</v>
-      </c>
-      <c r="F16" t="s">
-        <v>120</v>
-      </c>
-      <c r="G16">
-        <v>6</v>
-      </c>
-      <c r="H16">
-        <v>18</v>
-      </c>
-      <c r="I16">
-        <v>13</v>
-      </c>
-      <c r="J16" t="s">
-        <v>121</v>
-      </c>
       <c r="K16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L16" t="s">
         <v>61</v>
@@ -1412,163 +1352,13 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="O16">
         <v>3</v>
       </c>
       <c r="P16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>122</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>117</v>
-      </c>
-      <c r="D17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" t="s">
-        <v>123</v>
-      </c>
-      <c r="F17" t="s">
-        <v>124</v>
-      </c>
-      <c r="G17">
-        <v>6.5</v>
-      </c>
-      <c r="H17">
-        <v>19</v>
-      </c>
-      <c r="I17">
-        <v>14</v>
-      </c>
-      <c r="J17" t="s">
-        <v>125</v>
-      </c>
-      <c r="K17" t="s">
-        <v>122</v>
-      </c>
-      <c r="L17" t="s">
-        <v>61</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0.42</v>
-      </c>
-      <c r="O17">
-        <v>3</v>
-      </c>
-      <c r="P17">
         <v>8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" t="s">
-        <v>128</v>
-      </c>
-      <c r="E18" t="s">
-        <v>129</v>
-      </c>
-      <c r="F18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G18">
-        <v>9</v>
-      </c>
-      <c r="H18">
-        <v>24</v>
-      </c>
-      <c r="I18">
-        <v>15</v>
-      </c>
-      <c r="J18" t="s">
-        <v>131</v>
-      </c>
-      <c r="K18" t="s">
-        <v>126</v>
-      </c>
-      <c r="L18" t="s">
-        <v>61</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0.45</v>
-      </c>
-      <c r="O18">
-        <v>4</v>
-      </c>
-      <c r="P18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>127</v>
-      </c>
-      <c r="D19" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" t="s">
-        <v>133</v>
-      </c>
-      <c r="F19" t="s">
-        <v>134</v>
-      </c>
-      <c r="G19">
-        <v>10</v>
-      </c>
-      <c r="H19">
-        <v>26</v>
-      </c>
-      <c r="I19">
-        <v>16</v>
-      </c>
-      <c r="J19" t="s">
-        <v>135</v>
-      </c>
-      <c r="K19" t="s">
-        <v>132</v>
-      </c>
-      <c r="L19" t="s">
-        <v>61</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0.48</v>
-      </c>
-      <c r="O19">
-        <v>4</v>
-      </c>
-      <c r="P19">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1583,39 +1373,39 @@
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C1" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D1" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="E1" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F1" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="E2" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="F2" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
@@ -1623,13 +1413,13 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="D3">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1643,19 +1433,19 @@
         <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="D4">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1663,13 +1453,13 @@
         <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="D5">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1683,13 +1473,13 @@
         <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D6">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1703,13 +1493,13 @@
         <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="D7">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1723,13 +1513,13 @@
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="D8">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1743,19 +1533,19 @@
         <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="D9">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1763,13 +1553,13 @@
         <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="D10">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1783,13 +1573,13 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D11">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1803,13 +1593,13 @@
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="D12">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1823,13 +1613,13 @@
         <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="D13">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1843,13 +1633,13 @@
         <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="C14" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="D14">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1863,13 +1653,13 @@
         <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="D15">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1883,13 +1673,13 @@
         <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="D16">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1903,13 +1693,13 @@
         <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="D17">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1923,10 +1713,10 @@
         <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="D18">
         <v>0.36</v>
@@ -1943,10 +1733,10 @@
         <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C19" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D19">
         <v>0.62</v>
@@ -1963,10 +1753,10 @@
         <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="C20" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="D20">
         <v>0.7</v>
@@ -1983,10 +1773,10 @@
         <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="D21">
         <v>0.14</v>
@@ -2003,10 +1793,10 @@
         <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="D22">
         <v>0.22</v>
@@ -2023,10 +1813,10 @@
         <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="D23">
         <v>0.008</v>
@@ -2043,10 +1833,10 @@
         <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C24" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="D24">
         <v>0.35</v>
@@ -2063,10 +1853,10 @@
         <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C25" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D25">
         <v>0.5</v>
@@ -2083,10 +1873,10 @@
         <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="D26">
         <v>0.55</v>
@@ -2103,10 +1893,10 @@
         <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="D27">
         <v>0.18</v>
@@ -2123,10 +1913,10 @@
         <v>74</v>
       </c>
       <c r="B28" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="D28">
         <v>0.25</v>
@@ -2143,10 +1933,10 @@
         <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="C29" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="D29">
         <v>0.006</v>
@@ -2163,13 +1953,13 @@
         <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="D30">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2183,13 +1973,13 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="D31">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2203,13 +1993,13 @@
         <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C32" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="D32">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2223,13 +2013,13 @@
         <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C33" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="D33">
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2243,13 +2033,13 @@
         <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="D34">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2260,16 +2050,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="D35">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2280,16 +2070,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="D36">
-        <v>0.05</v>
+        <v>0.82</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2300,16 +2090,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D37">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2323,13 +2113,13 @@
         <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C38" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D38">
-        <v>0.32</v>
+        <v>0.1</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2343,13 +2133,13 @@
         <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D39">
-        <v>0.58</v>
+        <v>0.08</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2360,13 +2150,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="D40">
         <v>0.24</v>
@@ -2380,16 +2170,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B41" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D41">
-        <v>0.46</v>
+        <v>0.08</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2400,16 +2190,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C42" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D42">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2420,16 +2210,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="C43" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="D43">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2443,13 +2233,13 @@
         <v>88</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D44">
-        <v>0.28</v>
+        <v>0.12</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2463,13 +2253,13 @@
         <v>88</v>
       </c>
       <c r="B45" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C45" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="D45">
-        <v>0.68</v>
+        <v>0.012</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2480,16 +2270,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="C46" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="D46">
-        <v>0.52</v>
+        <v>0.25</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2500,16 +2290,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B47" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C47" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D47">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2520,16 +2310,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B48" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D48">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2540,16 +2330,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B49" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="C49" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D49">
-        <v>0.012</v>
+        <v>0.5</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2563,13 +2353,13 @@
         <v>92</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C50" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D50">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2580,36 +2370,36 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B51" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="D51">
-        <v>0.72</v>
+        <v>0.22</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B52" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="C52" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D52">
-        <v>0.78</v>
+        <v>0.55</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2620,16 +2410,16 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C53" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D53">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2640,16 +2430,16 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B54" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="C54" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D54">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2660,16 +2450,16 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B55" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="C55" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="D55">
-        <v>0.14</v>
+        <v>0.015</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2680,16 +2470,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="C56" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="D56">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2700,16 +2490,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B57" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="D57">
-        <v>0.015</v>
+        <v>0.65</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2720,16 +2510,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B58" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C58" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D58">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2740,16 +2530,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C59" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="D59">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2760,16 +2550,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B60" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C60" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D60">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2780,16 +2570,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="D61">
-        <v>0.2</v>
+        <v>0.018</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2800,16 +2590,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="C62" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="D62">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2820,16 +2610,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B63" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="D63">
-        <v>0.025</v>
+        <v>0.6</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2840,13 +2630,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B64" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C64" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D64">
         <v>0.22</v>
@@ -2860,16 +2650,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B65" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="C65" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="D65">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2880,16 +2670,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C66" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D66">
-        <v>0.48</v>
+        <v>0.08</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2900,16 +2690,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B67" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C67" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="D67">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2920,16 +2710,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="C68" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D68">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2940,16 +2730,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B69" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C69" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D69">
-        <v>0.1</v>
+        <v>0.52</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2960,16 +2750,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C70" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D70">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2980,16 +2770,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B71" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C71" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D71">
-        <v>0.58</v>
+        <v>0.1</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -3000,16 +2790,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B72" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="C72" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="D72">
-        <v>0.38</v>
+        <v>0.18</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -3020,16 +2810,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C73" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D73">
-        <v>0.25</v>
+        <v>0.025</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -3040,16 +2830,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B74" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="C74" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="D74">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3060,13 +2850,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B75" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="C75" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D75">
         <v>0.06</v>
@@ -3080,16 +2870,16 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B76" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C76" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D76">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3100,16 +2890,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B77" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C77" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D77">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3120,16 +2910,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B78" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="C78" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="D78">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3140,541 +2930,21 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B79" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="C79" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="D79">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E79">
         <v>0</v>
       </c>
       <c r="F79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>112</v>
-      </c>
-      <c r="B80" t="s">
-        <v>159</v>
-      </c>
-      <c r="C80" t="s">
-        <v>160</v>
-      </c>
-      <c r="D80">
-        <v>0.22</v>
-      </c>
-      <c r="E80">
-        <v>0</v>
-      </c>
-      <c r="F80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>112</v>
-      </c>
-      <c r="B81" t="s">
-        <v>161</v>
-      </c>
-      <c r="C81" t="s">
-        <v>162</v>
-      </c>
-      <c r="D81">
-        <v>0.14</v>
-      </c>
-      <c r="E81">
-        <v>0</v>
-      </c>
-      <c r="F81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>112</v>
-      </c>
-      <c r="B82" t="s">
-        <v>157</v>
-      </c>
-      <c r="C82" t="s">
-        <v>158</v>
-      </c>
-      <c r="D82">
-        <v>0.055</v>
-      </c>
-      <c r="E82">
-        <v>0</v>
-      </c>
-      <c r="F82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>116</v>
-      </c>
-      <c r="B83" t="s">
-        <v>147</v>
-      </c>
-      <c r="C83" t="s">
-        <v>148</v>
-      </c>
-      <c r="D83">
-        <v>0.16</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-      <c r="F83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>116</v>
-      </c>
-      <c r="B84" t="s">
-        <v>165</v>
-      </c>
-      <c r="C84" t="s">
-        <v>166</v>
-      </c>
-      <c r="D84">
-        <v>0.7</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>116</v>
-      </c>
-      <c r="B85" t="s">
-        <v>159</v>
-      </c>
-      <c r="C85" t="s">
-        <v>160</v>
-      </c>
-      <c r="D85">
-        <v>0.45</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-      <c r="F85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>116</v>
-      </c>
-      <c r="B86" t="s">
-        <v>153</v>
-      </c>
-      <c r="C86" t="s">
-        <v>154</v>
-      </c>
-      <c r="D86">
-        <v>0.25</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-      <c r="F86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>116</v>
-      </c>
-      <c r="B87" t="s">
-        <v>155</v>
-      </c>
-      <c r="C87" t="s">
-        <v>156</v>
-      </c>
-      <c r="D87">
-        <v>0.12</v>
-      </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
-      <c r="F87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>116</v>
-      </c>
-      <c r="B88" t="s">
-        <v>157</v>
-      </c>
-      <c r="C88" t="s">
-        <v>158</v>
-      </c>
-      <c r="D88">
-        <v>0.02</v>
-      </c>
-      <c r="E88">
-        <v>0</v>
-      </c>
-      <c r="F88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>122</v>
-      </c>
-      <c r="B89" t="s">
-        <v>147</v>
-      </c>
-      <c r="C89" t="s">
-        <v>148</v>
-      </c>
-      <c r="D89">
-        <v>0.15</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-      <c r="F89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>122</v>
-      </c>
-      <c r="B90" t="s">
-        <v>165</v>
-      </c>
-      <c r="C90" t="s">
-        <v>166</v>
-      </c>
-      <c r="D90">
-        <v>0.75</v>
-      </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-      <c r="F90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>122</v>
-      </c>
-      <c r="B91" t="s">
-        <v>159</v>
-      </c>
-      <c r="C91" t="s">
-        <v>160</v>
-      </c>
-      <c r="D91">
-        <v>0.52</v>
-      </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
-      <c r="F91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>122</v>
-      </c>
-      <c r="B92" t="s">
-        <v>153</v>
-      </c>
-      <c r="C92" t="s">
-        <v>154</v>
-      </c>
-      <c r="D92">
-        <v>0.18</v>
-      </c>
-      <c r="E92">
-        <v>0</v>
-      </c>
-      <c r="F92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>122</v>
-      </c>
-      <c r="B93" t="s">
-        <v>157</v>
-      </c>
-      <c r="C93" t="s">
-        <v>158</v>
-      </c>
-      <c r="D93">
-        <v>0.025</v>
-      </c>
-      <c r="E93">
-        <v>0</v>
-      </c>
-      <c r="F93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>126</v>
-      </c>
-      <c r="B94" t="s">
-        <v>147</v>
-      </c>
-      <c r="C94" t="s">
-        <v>148</v>
-      </c>
-      <c r="D94">
-        <v>0.14</v>
-      </c>
-      <c r="E94">
-        <v>0</v>
-      </c>
-      <c r="F94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>126</v>
-      </c>
-      <c r="B95" t="s">
-        <v>157</v>
-      </c>
-      <c r="C95" t="s">
-        <v>158</v>
-      </c>
-      <c r="D95">
-        <v>0.12</v>
-      </c>
-      <c r="E95">
-        <v>0</v>
-      </c>
-      <c r="F95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>126</v>
-      </c>
-      <c r="B96" t="s">
-        <v>163</v>
-      </c>
-      <c r="C96" t="s">
-        <v>164</v>
-      </c>
-      <c r="D96">
-        <v>0.1</v>
-      </c>
-      <c r="E96">
-        <v>0</v>
-      </c>
-      <c r="F96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>126</v>
-      </c>
-      <c r="B97" t="s">
-        <v>159</v>
-      </c>
-      <c r="C97" t="s">
-        <v>160</v>
-      </c>
-      <c r="D97">
-        <v>0.2</v>
-      </c>
-      <c r="E97">
-        <v>0</v>
-      </c>
-      <c r="F97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>126</v>
-      </c>
-      <c r="B98" t="s">
-        <v>165</v>
-      </c>
-      <c r="C98" t="s">
-        <v>166</v>
-      </c>
-      <c r="D98">
-        <v>0.18</v>
-      </c>
-      <c r="E98">
-        <v>0</v>
-      </c>
-      <c r="F98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>126</v>
-      </c>
-      <c r="B99" t="s">
-        <v>161</v>
-      </c>
-      <c r="C99" t="s">
-        <v>162</v>
-      </c>
-      <c r="D99">
-        <v>0.08</v>
-      </c>
-      <c r="E99">
-        <v>0</v>
-      </c>
-      <c r="F99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>132</v>
-      </c>
-      <c r="B100" t="s">
-        <v>147</v>
-      </c>
-      <c r="C100" t="s">
-        <v>148</v>
-      </c>
-      <c r="D100">
-        <v>0.12</v>
-      </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
-      <c r="F100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>132</v>
-      </c>
-      <c r="B101" t="s">
-        <v>157</v>
-      </c>
-      <c r="C101" t="s">
-        <v>158</v>
-      </c>
-      <c r="D101">
-        <v>0.14</v>
-      </c>
-      <c r="E101">
-        <v>0</v>
-      </c>
-      <c r="F101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>132</v>
-      </c>
-      <c r="B102" t="s">
-        <v>163</v>
-      </c>
-      <c r="C102" t="s">
-        <v>164</v>
-      </c>
-      <c r="D102">
-        <v>0.12</v>
-      </c>
-      <c r="E102">
-        <v>0</v>
-      </c>
-      <c r="F102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>132</v>
-      </c>
-      <c r="B103" t="s">
-        <v>159</v>
-      </c>
-      <c r="C103" t="s">
-        <v>160</v>
-      </c>
-      <c r="D103">
-        <v>0.16</v>
-      </c>
-      <c r="E103">
-        <v>0</v>
-      </c>
-      <c r="F103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>132</v>
-      </c>
-      <c r="B104" t="s">
-        <v>165</v>
-      </c>
-      <c r="C104" t="s">
-        <v>166</v>
-      </c>
-      <c r="D104">
-        <v>0.14</v>
-      </c>
-      <c r="E104">
-        <v>0</v>
-      </c>
-      <c r="F104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>132</v>
-      </c>
-      <c r="B105" t="s">
-        <v>161</v>
-      </c>
-      <c r="C105" t="s">
-        <v>162</v>
-      </c>
-      <c r="D105">
-        <v>0.06</v>
-      </c>
-      <c r="E105">
-        <v>0</v>
-      </c>
-      <c r="F105">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Excel/scavenge.xlsx
+++ b/Assets/Excel/scavenge.xlsx
@@ -6,6 +6,8 @@
     <sheet name="works" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="actions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="loot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="work_levels" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="action_levels" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -770,7 +772,6 @@
           <t>scavenge_gate_ergou</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -834,7 +835,6 @@
           <t>scavenge_gate_woodshed</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
@@ -898,7 +898,6 @@
           <t>scavenge_gate_fork</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
@@ -962,7 +961,6 @@
           <t>scavenge_gate_well</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1026,7 +1024,6 @@
           <t>scavenge_gate_chief</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1090,7 +1087,6 @@
           <t>scavenge_black_pine_trail</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>0</v>
       </c>
@@ -1154,7 +1150,6 @@
           <t>scavenge_black_pine_fallen</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -1218,7 +1213,6 @@
           <t>scavenge_black_pine_shrine</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -1282,7 +1276,6 @@
           <t>scavenge_black_pine_hunter</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1346,7 +1339,6 @@
           <t>scavenge_black_pine_stream</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1410,7 +1402,6 @@
           <t>scavenge_black_pine_bandit</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1474,7 +1465,6 @@
           <t>scavenge_old_road_camp</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1538,7 +1528,6 @@
           <t>scavenge_old_road_station</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -1602,7 +1591,6 @@
           <t>scavenge_old_road_bridge</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -3699,4 +3687,2640 @@
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B162"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>升到下级所需经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3181</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>3514</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3862</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4353</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4480</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5006</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5420</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5562</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>5705</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5850</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5997</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>6146</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6296</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6448</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>6602</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6758</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>6916</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>7076</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>7237</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>7565</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>7732</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8070</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8242</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8416</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8592</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8770</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8949</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>9130</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9313</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>9498</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9684</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>9872</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>10062</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>10254</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>10448</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>10841</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>11241</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>11444</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>11648</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>11854</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>12062</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>12272</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>12484</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>12698</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>12913</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>13130</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>13349</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>13570</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>13792</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>14016</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>14242</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>14470</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>14932</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>15165</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>15400</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>15637</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>15876</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>16116</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>16358</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>16602</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>16848</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>17096</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>17346</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>17597</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>17850</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>18105</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>18362</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>18620</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>18880</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>19142</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>19406</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>19672</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>19940</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>20209</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>20480</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>20753</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>21028</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>21304</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>21582</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>21862</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>22144</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>22428</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>22714</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>23001</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>23290</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>23581</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>23874</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>24168</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>24464</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>24762</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>25062</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>25364</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>25668</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>25973</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B162"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>升到下级所需经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3181</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>3514</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3862</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4353</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4480</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5006</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5420</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5562</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>5705</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5850</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5997</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>6146</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6296</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6448</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>6602</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6758</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>6916</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>7076</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>7237</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>7565</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>7732</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8070</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8242</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8416</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8592</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8770</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8949</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>9130</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9313</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>9498</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9684</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>9872</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>10062</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>10254</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>10448</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>10841</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>11241</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>11444</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>11648</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>11854</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>12062</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>12272</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>12484</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>12698</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>12913</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>13130</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>13349</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>13570</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>13792</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>14016</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>14242</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>14470</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>14932</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>15165</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>15400</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>15637</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>15876</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>16116</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>16358</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>16602</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>16848</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>17096</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>17346</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>17597</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>17850</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>18105</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>18362</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>18620</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>18880</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>19142</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>19406</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>19672</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>19940</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>20209</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>20480</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>20753</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>21028</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>21304</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>21582</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>21862</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>22144</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>22428</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>22714</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>23001</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>23290</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>23581</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>23874</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>24168</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>24464</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>24762</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>25062</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>25364</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>25668</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>25973</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
 </file>
--- a/Assets/Excel/scavenge.xlsx
+++ b/Assets/Excel/scavenge.xlsx
@@ -443,22 +443,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>地区熟练度基数</t>
+          <t>动作熟练度基数</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>地区熟练度每级增量</t>
+          <t>动作熟练度每级增量</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否加工作XP(1/0)</t>
+          <t>是否加总等级XP(1/0)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>是否加地区XP(1/0)</t>
+          <t>是否加动作熟练度XP(1/0)</t>
         </is>
       </c>
     </row>
@@ -490,12 +490,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>sceneXpBase</t>
+          <t>actionXpBase</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>sceneXpPerLevel</t>
+          <t>actionXpPerLevel</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>grantSceneXp</t>
+          <t>grantActionXp</t>
         </is>
       </c>
     </row>
